--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -400,20 +400,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L57"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="43.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,19 +456,2142 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>No tasks yet</v>
+        <v>sklearn</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D2" t="str">
+        <v>High</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G2" t="str">
+        <v>In Progress</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>sklearn.base</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D3" t="str">
+        <v>High</v>
+      </c>
+      <c r="E3" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Practice</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>sklearn.calibration</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D4" t="str">
+        <v>High</v>
+      </c>
+      <c r="E4" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G4" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>sklearn.callback</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D5" t="str">
+        <v>High</v>
+      </c>
+      <c r="E5" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G5" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>sklearn.cluster</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D6" t="str">
+        <v>High</v>
+      </c>
+      <c r="E6" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G6" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>sklearn.compose</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D7" t="str">
+        <v>High</v>
+      </c>
+      <c r="E7" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G7" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>sklearn.covariance</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D8" t="str">
+        <v>High</v>
+      </c>
+      <c r="E8" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G8" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>sklearn.cross_decomposition</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D9" t="str">
+        <v>High</v>
+      </c>
+      <c r="E9" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G9" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>sklearn.datasets</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D10" t="str">
+        <v>High</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G10" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>sklearn.decomposition</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D11" t="str">
+        <v>High</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G11" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>sklearn.discriminant_analysis</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D12" t="str">
+        <v>High</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G12" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>sklearn.dummy</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D13" t="str">
+        <v>High</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G13" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>sklearn.ensemble</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D14" t="str">
+        <v>High</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G14" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>sklearn.exceptions</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D15" t="str">
+        <v>High</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G15" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>sklearn.experimental</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D16" t="str">
+        <v>High</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G16" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>sklearn.feature_extraction</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D17" t="str">
+        <v>High</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G17" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>sklearn.feature_selection</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D18" t="str">
+        <v>High</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G18" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>sklearn.frozen</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D19" t="str">
+        <v>High</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G19" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>sklearn.gaussian_process</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D20" t="str">
+        <v>High</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G20" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>sklearn.impute</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D21" t="str">
+        <v>High</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G21" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>sklearn.inspection</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D22" t="str">
+        <v>High</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G22" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>sklearn.isotonic</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D23" t="str">
+        <v>High</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G23" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>sklearn.kernel_approximation</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D24" t="str">
+        <v>High</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G24" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>sklearn.kernel_ridge</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D25" t="str">
+        <v>High</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G25" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>sklearn.linear_model</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D26" t="str">
+        <v>High</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G26" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>sklearn.manifold</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D27" t="str">
+        <v>High</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G27" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>sklearn.metrics</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D28" t="str">
+        <v>High</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G28" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>sklearn.mixture</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D29" t="str">
+        <v>High</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G29" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>sklearn.model_selection</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D30" t="str">
+        <v>High</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G30" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>sklearn.multiclass</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D31" t="str">
+        <v>High</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G31" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>sklearn.multioutput</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D32" t="str">
+        <v>High</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G32" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>sklearn.naive_bayes</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D33" t="str">
+        <v>High</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G33" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>sklearn.neighbors</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D34" t="str">
+        <v>High</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G34" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>sklearn.neural_network</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D35" t="str">
+        <v>High</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G35" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>sklearn.pipeline</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D36" t="str">
+        <v>High</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G36" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>sklearn.preprocessing</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D37" t="str">
+        <v>High</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G37" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>sklearn.random_projection</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D38" t="str">
+        <v>High</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G38" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>sklearn.semi_supervised</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D39" t="str">
+        <v>High</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G39" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>sklearn.svm</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D40" t="str">
+        <v>High</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G40" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>sklearn.tree</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D41" t="str">
+        <v>High</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G41" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>sklearn.utils</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="D42" t="str">
+        <v>High</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G42" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Supervised learning</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D43" t="str">
+        <v>High</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G43" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Unsupervised learning</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D44" t="str">
+        <v>High</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G44" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Model selection and evaluation</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D45" t="str">
+        <v>High</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G45" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Metadata Routing</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D46" t="str">
+        <v>High</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G46" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Inspection</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D47" t="str">
+        <v>High</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G47" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Visualizations</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D48" t="str">
+        <v>High</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G48" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Callbacks</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D49" t="str">
+        <v>High</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G49" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Dataset transformations</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D50" t="str">
+        <v>High</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G50" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Dataset loading utilities</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D51" t="str">
+        <v>High</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G51" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Computing with scikit-learn</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D52" t="str">
+        <v>High</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G52" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Model persistence</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D53" t="str">
+        <v>High</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G53" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Common pitfalls and recommended practices</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D54" t="str">
+        <v>High</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G54" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Data Interoperability</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D55" t="str">
+        <v>High</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G55" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Choosing the right estimator</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D56" t="str">
+        <v>High</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G56" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>External Resources, Videos and Talks</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="D57" t="str">
+        <v>High</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G57" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Aug 8, 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L57"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -560,18 +2683,56 @@
         <v>0%</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-08-09</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3" t="str">
+        <v>0%</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
@@ -581,7 +2742,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,12 +2782,77 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>No epics yet</v>
+        <v>Scikit-Learn/ API</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>High</v>
+      </c>
+      <c r="D2">
+        <v>41</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>39</v>
+      </c>
+      <c r="J2" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Aug 8, 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Scikit-Learn/ User Guide</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>High</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>15</v>
+      </c>
+      <c r="J3" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Aug 8, 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -400,21 +400,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M37"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,24 +460,1495 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>No tasks yet</v>
+        <v>Installation Guide</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G2" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L2" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M2" t="str">
+        <v>mskjmm1ia28u3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Quick Start</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E3" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G3" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L3" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M3" t="str">
+        <v>mskjmm1i9x9ut</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Python Quick Start</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E4" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G4" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L4" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M4" t="str">
+        <v>mskjmm1i0an4d</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Features</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E5" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G5" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L5" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M5" t="str">
+        <v>mskjmm1ir8uys</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Experiments</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E6" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G6" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L6" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M6" t="str">
+        <v>mskjmm1in1491</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E7" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G7" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L7" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M7" t="str">
+        <v>mskjmm1iz5s6s</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Parameters Tuning</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E8" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G8" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L8" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M8" t="str">
+        <v>mskjmm1iy83x2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>C API</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G9" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L9" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M9" t="str">
+        <v>mskjmm1iahx06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Python API</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G10" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L10" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M10" t="str">
+        <v>mskjmm1il6vzq</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>R API</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G11" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L11" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M11" t="str">
+        <v>mskjmm1idpwev</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Distributed Learning Guide</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G12" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L12" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M12" t="str">
+        <v>mskjmm1irytor</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>GPU Tutorial</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E13" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G13" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L13" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M13" t="str">
+        <v>mskjmm1ijlwch</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Advanced Topics</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E14" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G14" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L14" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M14" t="str">
+        <v>mskjmm1izawzv</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>FAQ</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G15" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L15" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M15" t="str">
+        <v>mskjmm1i5vg3y</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Development Guide</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>LightGBM</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G16" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L16" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M16" t="str">
+        <v>mskjmm1ibeckq</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Installation Guide</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E17" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G17" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L17" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M17" t="str">
+        <v>mskjuazrvir8z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Building From Source</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E18" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G18" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L18" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M18" t="str">
+        <v>mskjuazrg15tu</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Get Started with XGBoost</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E19" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G19" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L19" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M19" t="str">
+        <v>mskjuazrw6ksx</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E20" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G20" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L20" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M20" t="str">
+        <v>mskjuazrdkxmj</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Frequently Asked Questions</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G21" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L21" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M21" t="str">
+        <v>mskjuazrh7x1j</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>GPU Support</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E22" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G22" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L22" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M22" t="str">
+        <v>mskjuazrqr7t0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>XGBoost Parameters</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E23" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G23" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L23" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M23" t="str">
+        <v>mskjuazruu4xz</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Prediction</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E24" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G24" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L24" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M24" t="str">
+        <v>mskjuazr7izui</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Tree Methods</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E25" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G25" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L25" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M25" t="str">
+        <v>mskjuazrk3kog</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Python Package</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G26" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L26" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M26" t="str">
+        <v>mskjuazr76k5n</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>R Package</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G27" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L27" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M27" t="str">
+        <v>mskjuazrr55s1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>JVM Package</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G28" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L28" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M28" t="str">
+        <v>mskjuazr0gaye</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Ruby Package</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G29" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L29" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M29" t="str">
+        <v>mskjuazrqqxe7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Swift Package</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G30" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L30" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M30" t="str">
+        <v>mskjuazrf8qko</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Julia Package</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G31" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L31" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M31" t="str">
+        <v>mskjuazrhf6l1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>C Package</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G32" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L32" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M32" t="str">
+        <v>mskjuazr6y2w1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>C++ Interface</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G33" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L33" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M33" t="str">
+        <v>mskjuazr1qa1k</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Security disclosure</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G34" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L34" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M34" t="str">
+        <v>mskjuazrjvhms</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Contribute to XGBoost</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G35" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L35" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M35" t="str">
+        <v>mskjuazrxonbt</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Release Notes</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G36" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L36" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M36" t="str">
+        <v>mskjuazr4b0ct</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>scikit-learn/API</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>scikit-learn</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E37" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F37" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G37" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L37" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="M37" t="str">
+        <v>mskk12tpxnz6q</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M37"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
@@ -486,7 +1957,7 @@
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
     <col min="11" max="11" width="10.83203125" customWidth="1"/>
     <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,19 +2003,96 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>No sprints yet</v>
+        <v>SPR-2026-W32</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-08-02</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-08-07</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M2" t="str">
+        <v>mskjfzjtplkth</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="F3">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>18</v>
+      </c>
+      <c r="L3" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M3" t="str">
+        <v>mskjojd2g5ua7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -556,8 +2104,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,31 +2148,140 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>No epics yet</v>
+        <v>LightGBM</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>Low</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>15</v>
+      </c>
+      <c r="J2" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K2" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L2" t="str">
+        <v>mskjl8cuwbnzs</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>20</v>
+      </c>
+      <c r="J3" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K3" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L3" t="str">
+        <v>mskjtuixm69sd</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>scikit-learn</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K4" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="L4" t="str">
+        <v>mskk074pigdwg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K10"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="54.83203125" customWidth="1"/>
+    <col min="2" max="2" width="55.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,12 +2321,353 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>No subtasks yet</v>
+        <v>Introduction to Boosted Trees</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D2" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F2" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K2" t="str">
+        <v>mskjvz8axp7bw</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Introduction to Model IO</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D3" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E3" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F3" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K3" t="str">
+        <v>mskjw7zqqol4f</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Slicing Models</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D4" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E4" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F4" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K4" t="str">
+        <v>mskjwecwnzinb</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Learning to Rank</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D5" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E5" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F5" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K5" t="str">
+        <v>mskjwjhp0kajz</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DART</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D6" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E6" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F6" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K6" t="str">
+        <v>mskjwo8nvlf63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Monotonic Constraints</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D7" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E7" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F7" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K7" t="str">
+        <v>mskjwtl16gyyh</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>🟥 Phase 1: Must-Know (The Core Foundation)</v>
+      </c>
+      <c r="B8" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `sklearn.pipeline`
+- `sklearn.compose`
+- `sklearn.preprocessing`
+- `sklearn.impute`
+- `sklearn.model_selection`
+- `sklearn.metrics`
+- `sklearn.linear_model`
+- `sklearn.tree`
+- `sklearn.dummy`</v>
+      </c>
+      <c r="C8" t="str">
+        <v>scikit-learn/API</v>
+      </c>
+      <c r="D8" t="str">
+        <v>scikit-learn</v>
+      </c>
+      <c r="E8" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F8" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K8" t="str">
+        <v>mskk2136wm2x1</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>🟨 Phase 2: Next Learn (The Production Heavyweights)</v>
+      </c>
+      <c r="B9" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `sklearn.ensemble`
+- `sklearn.feature_selection`
+- `sklearn.datasets`
+- `sklearn.base`
+- `sklearn.utils`
+- `sklearn.neighbors`
+- `sklearn.naive_bayes`
+- `sklearn.exceptions`</v>
+      </c>
+      <c r="C9" t="str">
+        <v>scikit-learn/API</v>
+      </c>
+      <c r="D9" t="str">
+        <v>scikit-learn</v>
+      </c>
+      <c r="E9" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F9" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K9" t="str">
+        <v>mskk2fgb7cnrq</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>🟩 Phase 3: Last Learn (Specialized &amp; Advanced)</v>
+      </c>
+      <c r="B10" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `sklearn.cluster`
+- `sklearn.decomposition`
+- `sklearn.inspect`
+- `sklearn.feature_extraction`
+- `sklearn.calibration`
+- `sklearn.svm`
+- `sklearn.manifold`
+- `sklearn.mixture`
+- `sklearn.covariance`
+- `sklearn.cross_decomposition`
+- `sklearn.semi_supervised`
+- `sklearn.neural_network`
+- `sklearn.discriminant_analysis`
+- `sklearn.isotonic`
+- `sklearn.kernel_approximation`
+- `sklearn.random_projection`
+- `sklearn.callback`</v>
+      </c>
+      <c r="C10" t="str">
+        <v>scikit-learn/API</v>
+      </c>
+      <c r="D10" t="str">
+        <v>scikit-learn</v>
+      </c>
+      <c r="E10" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F10" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>8 Aug 2026</v>
+      </c>
+      <c r="K10" t="str">
+        <v>mskk2w5rmle9n</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -412,8 +412,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -490,10 +490,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -531,10 +531,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -572,10 +572,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -613,10 +613,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -695,10 +695,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -777,10 +777,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -818,10 +818,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -859,10 +859,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -941,10 +941,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -982,10 +982,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1023,10 +1023,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1064,10 +1064,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1105,10 +1105,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1146,10 +1146,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1351,10 +1351,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1392,10 +1392,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1433,10 +1433,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1556,10 +1556,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1638,10 +1638,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1679,10 +1679,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1720,10 +1720,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1884,10 +1884,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1925,10 +1925,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -2104,7 +2104,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2178,7 +2178,7 @@
         <v>0%</v>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
         <v>mskjl8cuwbnzs</v>
@@ -2216,7 +2216,7 @@
         <v>0%</v>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
         <v>mskjtuixm69sd</v>
@@ -2254,7 +2254,7 @@
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
         <v>mskk074pigdwg</v>
@@ -2280,7 +2280,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2348,7 +2348,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -2383,7 +2383,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -2418,7 +2418,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -2488,7 +2488,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -2523,7 +2523,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -2566,7 +2566,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -2608,7 +2608,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -2659,7 +2659,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -412,8 +412,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -490,10 +490,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -531,10 +531,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -572,10 +572,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -613,10 +613,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -695,10 +695,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -777,10 +777,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -818,10 +818,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -859,10 +859,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -941,10 +941,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -982,10 +982,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1023,10 +1023,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1064,10 +1064,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1105,10 +1105,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1146,10 +1146,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1351,10 +1351,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1392,10 +1392,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1433,10 +1433,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1556,10 +1556,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1638,10 +1638,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1679,10 +1679,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1720,10 +1720,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1884,10 +1884,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1925,10 +1925,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -2092,7 +2092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:Q4"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -2104,8 +2104,13 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2143,6 +2148,21 @@
         <v>Created</v>
       </c>
       <c r="L1" t="str">
+        <v>Schedule Enabled</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Schedule Label</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Schedule Start</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Schedule End</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Scheduled Task IDs</v>
+      </c>
+      <c r="Q1" t="str">
         <v>__id</v>
       </c>
     </row>
@@ -2178,9 +2198,24 @@
         <v>0%</v>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v>mskjl8cuwbnzs</v>
       </c>
     </row>
@@ -2216,9 +2251,24 @@
         <v>0%</v>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="O3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
         <v>mskjtuixm69sd</v>
       </c>
     </row>
@@ -2254,15 +2304,30 @@
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
         <v>mskk074pigdwg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2280,7 +2345,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2348,7 +2413,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -2383,7 +2448,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -2418,7 +2483,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -2453,7 +2518,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -2488,7 +2553,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -2523,7 +2588,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -2566,7 +2631,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -2608,7 +2673,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -2659,7 +2724,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -2207,10 +2207,10 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>04:00</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>06:00</v>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -2313,10 +2313,10 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>15:00</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>18:00</v>
       </c>
       <c r="P4" t="str">
         <v/>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -2207,10 +2207,10 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>04:00</v>
+        <v>05:00</v>
       </c>
       <c r="O2" t="str">
-        <v>06:00</v>
+        <v>07:00</v>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -2313,10 +2313,10 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>15:00</v>
+        <v>11:00</v>
       </c>
       <c r="O4" t="str">
-        <v>18:00</v>
+        <v>13:00</v>
       </c>
       <c r="P4" t="str">
         <v/>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -412,8 +412,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -478,7 +478,7 @@
         <v>2026-08</v>
       </c>
       <c r="G2" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H2" t="str">
         <v>Low</v>
@@ -490,10 +490,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -519,7 +519,7 @@
         <v>2026-08</v>
       </c>
       <c r="G3" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H3" t="str">
         <v>Low</v>
@@ -531,10 +531,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -560,7 +560,7 @@
         <v>2026-08</v>
       </c>
       <c r="G4" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H4" t="str">
         <v>Low</v>
@@ -572,10 +572,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -601,7 +601,7 @@
         <v>2026-08</v>
       </c>
       <c r="G5" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H5" t="str">
         <v>Low</v>
@@ -613,10 +613,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -642,7 +642,7 @@
         <v>2026-08</v>
       </c>
       <c r="G6" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H6" t="str">
         <v>Low</v>
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -683,7 +683,7 @@
         <v>2026-08</v>
       </c>
       <c r="G7" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H7" t="str">
         <v>Low</v>
@@ -695,10 +695,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -724,7 +724,7 @@
         <v>2026-08</v>
       </c>
       <c r="G8" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H8" t="str">
         <v>Low</v>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -777,10 +777,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -818,10 +818,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -859,10 +859,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -941,10 +941,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -970,7 +970,7 @@
         <v>2026-08</v>
       </c>
       <c r="G14" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H14" t="str">
         <v>Low</v>
@@ -982,10 +982,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1023,10 +1023,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1064,10 +1064,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1105,10 +1105,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1146,10 +1146,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1351,10 +1351,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1392,10 +1392,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1433,10 +1433,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1556,10 +1556,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1638,10 +1638,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1679,10 +1679,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1720,10 +1720,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1884,10 +1884,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1925,10 +1925,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -2062,7 +2062,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2074,10 +2074,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L3" t="str">
-        <v>0%</v>
+        <v>44%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -2104,7 +2104,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -2180,7 +2180,7 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2192,13 +2192,13 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J2" t="str">
-        <v>0%</v>
+        <v>53%</v>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -2251,7 +2251,7 @@
         <v>0%</v>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -2304,7 +2304,7 @@
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -2345,7 +2345,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2413,7 +2413,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -2483,7 +2483,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -2518,7 +2518,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -2553,7 +2553,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -2588,7 +2588,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -2631,7 +2631,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -2673,7 +2673,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -2724,7 +2724,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -412,8 +412,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -490,10 +490,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -531,10 +531,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -572,10 +572,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -613,10 +613,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -695,10 +695,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -777,10 +777,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -818,10 +818,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -859,10 +859,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -941,10 +941,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -982,10 +982,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1023,10 +1023,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1064,10 +1064,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1105,10 +1105,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1146,10 +1146,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1351,10 +1351,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1392,10 +1392,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1433,10 +1433,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1556,10 +1556,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1638,10 +1638,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1679,10 +1679,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1720,10 +1720,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1884,10 +1884,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1925,10 +1925,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -2104,7 +2104,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -2198,7 +2198,7 @@
         <v>53%</v>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -2251,7 +2251,7 @@
         <v>0%</v>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -2260,10 +2260,10 @@
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>08:00</v>
+        <v>09:30</v>
       </c>
       <c r="O3" t="str">
-        <v>10:00</v>
+        <v>12:00</v>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -2304,7 +2304,7 @@
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -2334,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K15"/>
   <cols>
     <col min="1" max="1" width="54.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
@@ -2413,7 +2413,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -2483,7 +2483,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -2518,7 +2518,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -2553,7 +2553,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -2588,7 +2588,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -2631,7 +2631,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -2673,7 +2673,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -2724,15 +2724,190 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Feature Interaction Constraints</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D11" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E11" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F11" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K11" t="str">
+        <v>msmnd1859wbzh</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Survival Analysis with Accelerated Failure Time</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D12" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E12" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F12" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K12" t="str">
+        <v>msmnd9ppyvwo0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Categorical Data</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D13" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E13" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F13" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K13" t="str">
+        <v>msmndgl7h0wic</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Multiple Outputs</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D14" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E14" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F14" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K14" t="str">
+        <v>msmndnshe7g32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Random Forests(TM) in XGBoost</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D15" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E15" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F15" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K15" t="str">
+        <v>msmndu14o94q4</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -408,12 +408,12 @@
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -490,10 +490,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -531,10 +531,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -572,10 +572,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -613,10 +613,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -695,10 +695,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -777,10 +777,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -818,10 +818,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -859,10 +859,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -941,10 +941,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -982,10 +982,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1023,10 +1023,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1064,10 +1064,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1093,7 +1093,7 @@
         <v>2026-08</v>
       </c>
       <c r="G17" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H17" t="str">
         <v>Low</v>
@@ -1105,10 +1105,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1134,7 +1134,7 @@
         <v>2026-08</v>
       </c>
       <c r="G18" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H18" t="str">
         <v>Low</v>
@@ -1146,10 +1146,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1175,7 +1175,7 @@
         <v>2026-08</v>
       </c>
       <c r="G19" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H19" t="str">
         <v>Low</v>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1216,7 +1216,7 @@
         <v>2026-08</v>
       </c>
       <c r="G20" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H20" t="str">
         <v>Low</v>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1339,7 +1339,7 @@
         <v>2026-08</v>
       </c>
       <c r="G23" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H23" t="str">
         <v>Low</v>
@@ -1351,10 +1351,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1380,7 +1380,7 @@
         <v>2026-08</v>
       </c>
       <c r="G24" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H24" t="str">
         <v>Low</v>
@@ -1392,10 +1392,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1421,7 +1421,7 @@
         <v>2026-08</v>
       </c>
       <c r="G25" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H25" t="str">
         <v>Low</v>
@@ -1433,10 +1433,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1556,10 +1556,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1638,10 +1638,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1679,10 +1679,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1720,10 +1720,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1884,10 +1884,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1913,7 +1913,7 @@
         <v>2026-08</v>
       </c>
       <c r="G37" t="str">
-        <v>To Do</v>
+        <v>In Progress</v>
       </c>
       <c r="H37" t="str">
         <v>Medium</v>
@@ -1925,10 +1925,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -2062,10 +2062,10 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2074,10 +2074,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L3" t="str">
-        <v>44%</v>
+        <v>83%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -2104,7 +2104,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -2198,7 +2198,7 @@
         <v>53%</v>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -2233,7 +2233,7 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2245,13 +2245,13 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J3" t="str">
-        <v>0%</v>
+        <v>35%</v>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2298,13 +2298,13 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="str">
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>11:00</v>
+        <v>12:00</v>
       </c>
       <c r="O4" t="str">
         <v>13:00</v>
@@ -2345,7 +2345,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2401,7 +2401,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F2" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G2" t="str">
         <v>Low</v>
@@ -2413,7 +2413,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -2436,7 +2436,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F3" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G3" t="str">
         <v>Low</v>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -2471,7 +2471,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F4" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G4" t="str">
         <v>Medium</v>
@@ -2483,7 +2483,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -2506,7 +2506,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F5" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G5" t="str">
         <v>Medium</v>
@@ -2518,7 +2518,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -2541,7 +2541,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F6" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G6" t="str">
         <v>Medium</v>
@@ -2553,7 +2553,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -2576,7 +2576,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F7" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G7" t="str">
         <v>Medium</v>
@@ -2588,7 +2588,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -2619,7 +2619,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F8" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G8" t="str">
         <v>Medium</v>
@@ -2631,7 +2631,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -2673,7 +2673,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -2724,7 +2724,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -2747,7 +2747,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F11" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G11" t="str">
         <v>Low</v>
@@ -2759,7 +2759,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -2782,7 +2782,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F12" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G12" t="str">
         <v>Medium</v>
@@ -2794,7 +2794,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -2817,7 +2817,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F13" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G13" t="str">
         <v>Medium</v>
@@ -2829,7 +2829,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -2852,7 +2852,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F14" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G14" t="str">
         <v>Medium</v>
@@ -2864,7 +2864,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -2887,7 +2887,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F15" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G15" t="str">
         <v>Medium</v>
@@ -2899,7 +2899,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -400,9 +400,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M94"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
@@ -413,7 +413,7 @@
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
     <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -490,10 +490,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -531,10 +531,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -572,10 +572,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -613,10 +613,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -695,10 +695,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -777,10 +777,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -818,10 +818,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -859,10 +859,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -941,10 +941,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -982,10 +982,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1023,10 +1023,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1064,10 +1064,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1105,10 +1105,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1146,10 +1146,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1351,10 +1351,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1392,10 +1392,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1433,10 +1433,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1556,10 +1556,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1638,10 +1638,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1679,10 +1679,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1720,10 +1720,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1884,10 +1884,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>scikit-learn</v>
+        <v>Scikit-Learn</v>
       </c>
       <c r="D37" t="str">
         <v>Medium</v>
@@ -1925,18 +1925,2355 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Install</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G38" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L38" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M38" t="str">
+        <v>msokvqo38bfww</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Quickstart</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G39" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L39" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M39" t="str">
+        <v>msokvqo3tpfld</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Local server</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G40" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L40" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M40" t="str">
+        <v>msokvqo323mt3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Thinking in LangGraph</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G41" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L41" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M41" t="str">
+        <v>msokvqo3fjm2f</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Workflows + agents</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G42" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L42" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M42" t="str">
+        <v>msokvqo34hlxf</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Persistence</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G43" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L43" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M43" t="str">
+        <v>msokwhmdho1q0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Checkpointers</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G44" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L44" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M44" t="str">
+        <v>msokwhmdegi75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Stores</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G45" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L45" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M45" t="str">
+        <v>msokwhmdcolem</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Fault tolerance</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G46" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L46" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M46" t="str">
+        <v>msokwhmd3im81</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Event streaming</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G47" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L47" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M47" t="str">
+        <v>msokwhmdy3sam</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Streaming</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G48" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L48" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M48" t="str">
+        <v>msokwhmdnrh8d</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Interrupts</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G49" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L49" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M49" t="str">
+        <v>msokwhmdjqudo</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Time travel</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G50" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L50" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M50" t="str">
+        <v>msokwhmdew0dw</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G51" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L51" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M51" t="str">
+        <v>msokwhmdul4ig</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Subgraphs</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G52" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L52" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M52" t="str">
+        <v>msokwhmdgbas5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Application structure</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G53" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L53" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M53" t="str">
+        <v>msokxlxs06a9x</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Test</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G54" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L54" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M54" t="str">
+        <v>msokxlxs42f77</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Backward compatibility</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G55" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L55" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M55" t="str">
+        <v>msokxlxs6xyeg</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>LangSmith Studio</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G56" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L56" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M56" t="str">
+        <v>msokxlxs7dltq</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Agent Chat UI</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G57" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L57" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M57" t="str">
+        <v>msokxlxsgvc7b</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G58" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L58" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M58" t="str">
+        <v>msokxlxsrox0v</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>LangSmith Observability</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G59" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L59" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M59" t="str">
+        <v>msokxlxsbwhdd</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Overview</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G60" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L60" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M60" t="str">
+        <v>msokxx7vw4unh</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Graph execution</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G61" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L61" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M61" t="str">
+        <v>msokxx7vcpo7d</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Custom stream channels</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G62" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L62" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M62" t="str">
+        <v>msokxx7vxd5a6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Install</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G63" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L63" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M63" t="str">
+        <v>msol0sqedwrwb</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Quickstart</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G64" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L64" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M64" t="str">
+        <v>msol0sqengvk7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Changelog</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G65" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L65" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M65" t="str">
+        <v>msol0sqeuws7d</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Philosophy</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G66" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L66" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M66" t="str">
+        <v>msol0sqekcfzc</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Agents</v>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G67" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L67" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M67" t="str">
+        <v>msol0sqemrzds</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Models</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G68" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L68" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M68" t="str">
+        <v>msol0sqepq0ch</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Messages</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G69" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L69" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M69" t="str">
+        <v>msol0sqe12vt4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Tools</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G70" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L70" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M70" t="str">
+        <v>msol0sqelotvw</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Short-term memory</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G71" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L71" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M71" t="str">
+        <v>msol0sqe3ckax</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Event streaming</v>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G72" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L72" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M72" t="str">
+        <v>msol0sqe7neja</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Streaming</v>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+      <c r="C73" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G73" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L73" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M73" t="str">
+        <v>msol0sqemccjp</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Structured output</v>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G74" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L74" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M74" t="str">
+        <v>msol0sqei4fpl</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Overview</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G75" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L75" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M75" t="str">
+        <v>msol0sqe37ejp</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Prebuilt middleware</v>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G76" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L76" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M76" t="str">
+        <v>msol0sqe2tdno</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Custom middleware</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G77" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L77" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M77" t="str">
+        <v>msol0sqe3wknl</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Overview</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G78" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L78" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M78" t="str">
+        <v>msol0sqejzchq</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Patterns</v>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G79" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L79" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M79" t="str">
+        <v>msol0sqet2uhb</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Integrations</v>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G80" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L80" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M80" t="str">
+        <v>msol0sqe5wsbz</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Guardrails</v>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G81" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L81" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M81" t="str">
+        <v>msol0sqezkuii</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Runtime</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G82" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L82" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M82" t="str">
+        <v>msol0sqe4p67x</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Context engineering</v>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G83" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L83" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M83" t="str">
+        <v>msol0sqehxbfj</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Model Context Protocol (MCP)</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G84" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L84" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M84" t="str">
+        <v>msol0sqe6dg2v</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Human-in-the-loop</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G85" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L85" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M85" t="str">
+        <v>msol0sqewy04g</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Multi-agent</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G86" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L86" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M86" t="str">
+        <v>msol0sqee580t</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Retrieval</v>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G87" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L87" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M87" t="str">
+        <v>msol0sqeiznyn</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Long-term memory</v>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+      <c r="C88" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G88" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L88" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M88" t="str">
+        <v>msol0sqeohz5d</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>LangSmith Studio</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G89" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L89" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M89" t="str">
+        <v>msol0sqepq9bm</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Test</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G90" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L90" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M90" t="str">
+        <v>msol0sqepn626</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Agent Chat UI</v>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G91" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L91" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M91" t="str">
+        <v>msol0sqe28q4z</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G92" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L92" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M92" t="str">
+        <v>msol0sqe56y72</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G93" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L93" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M93" t="str">
+        <v>msol0sqeyukhl</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Parse</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>LlamaIndex</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G94" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L94" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="M94" t="str">
+        <v>msol2k62oicjg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M94"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2092,7 +4429,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q7"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -2198,7 +4535,7 @@
         <v>53%</v>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -2207,10 +4544,10 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>05:00</v>
+        <v/>
       </c>
       <c r="O2" t="str">
-        <v>07:00</v>
+        <v/>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -2251,7 +4588,7 @@
         <v>35%</v>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -2260,10 +4597,10 @@
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>09:30</v>
+        <v/>
       </c>
       <c r="O3" t="str">
-        <v>12:00</v>
+        <v/>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -2274,7 +4611,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>scikit-learn</v>
+        <v>Scikit-Learn</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -2304,19 +4641,19 @@
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="O4" t="str">
         <v>12:00</v>
-      </c>
-      <c r="O4" t="str">
-        <v>13:00</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -2325,9 +4662,168 @@
         <v>mskk074pigdwg</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>LangGraph</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>25</v>
+      </c>
+      <c r="J5" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K5" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L5" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v>07:00</v>
+      </c>
+      <c r="O5" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="P5" t="str">
+        <v>mskjuazr6y2w1</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>msokv11v8pdah</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LangChain</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>31</v>
+      </c>
+      <c r="J6" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K6" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L6" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v>msokz90zh9nmn</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LlamaIndex</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K7" t="str">
+        <v>11 Aug 2026</v>
+      </c>
+      <c r="L7" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>msol2au4dexr8</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2345,7 +4841,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2413,7 +4909,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -2448,7 +4944,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -2483,7 +4979,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -2518,7 +5014,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -2553,7 +5049,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -2588,7 +5084,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -2613,7 +5109,7 @@
         <v>scikit-learn/API</v>
       </c>
       <c r="D8" t="str">
-        <v>scikit-learn</v>
+        <v>Scikit-Learn</v>
       </c>
       <c r="E8" t="str">
         <v>SPR-2026-W33</v>
@@ -2631,7 +5127,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -2655,13 +5151,13 @@
         <v>scikit-learn/API</v>
       </c>
       <c r="D9" t="str">
-        <v>scikit-learn</v>
+        <v>Scikit-Learn</v>
       </c>
       <c r="E9" t="str">
         <v>SPR-2026-W33</v>
       </c>
       <c r="F9" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G9" t="str">
         <v>Medium</v>
@@ -2673,7 +5169,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -2706,7 +5202,7 @@
         <v>scikit-learn/API</v>
       </c>
       <c r="D10" t="str">
-        <v>scikit-learn</v>
+        <v>Scikit-Learn</v>
       </c>
       <c r="E10" t="str">
         <v>SPR-2026-W33</v>
@@ -2724,7 +5220,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -2759,7 +5255,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -2794,7 +5290,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -2829,7 +5325,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -2864,7 +5360,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -2899,7 +5395,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -408,7 +408,7 @@
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
@@ -1913,7 +1913,7 @@
         <v>2026-08</v>
       </c>
       <c r="G37" t="str">
-        <v>In Progress</v>
+        <v>To Do</v>
       </c>
       <c r="H37" t="str">
         <v>Medium</v>
@@ -1928,7 +1928,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>10 Aug 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -4402,7 +4402,7 @@
         <v>15</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4411,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" t="str">
         <v>83%</v>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="str">
         <v>0%</v>
@@ -4644,19 +4644,19 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>10:00</v>
+        <v>04:00</v>
       </c>
       <c r="O4" t="str">
-        <v>12:00</v>
+        <v>06:00</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>mskk12tpxnz6q</v>
       </c>
       <c r="Q4" t="str">
         <v>mskk074pigdwg</v>
@@ -4697,19 +4697,19 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>07:00</v>
+        <v>08:00</v>
       </c>
       <c r="O5" t="str">
-        <v>09:00</v>
+        <v>10:00</v>
       </c>
       <c r="P5" t="str">
-        <v>mskjuazr6y2w1</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
         <v>msokv11v8pdah</v>
@@ -4756,10 +4756,10 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>10:00</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>12:00</v>
       </c>
       <c r="P6" t="str">
         <v/>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -412,8 +412,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -490,10 +490,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -531,10 +531,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -572,10 +572,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -613,10 +613,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -695,10 +695,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -777,10 +777,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -818,10 +818,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -859,10 +859,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -941,10 +941,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -982,10 +982,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1023,10 +1023,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1064,10 +1064,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1105,10 +1105,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1146,10 +1146,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1351,10 +1351,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1392,10 +1392,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1433,10 +1433,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1556,10 +1556,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1638,10 +1638,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1679,10 +1679,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1720,10 +1720,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1884,10 +1884,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1925,10 +1925,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -1966,10 +1966,10 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L38" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M38" t="str">
         <v>msokvqo38bfww</v>
@@ -2007,10 +2007,10 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L39" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M39" t="str">
         <v>msokvqo3tpfld</v>
@@ -2048,10 +2048,10 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L40" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M40" t="str">
         <v>msokvqo323mt3</v>
@@ -2089,10 +2089,10 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L41" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M41" t="str">
         <v>msokvqo3fjm2f</v>
@@ -2130,10 +2130,10 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L42" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M42" t="str">
         <v>msokvqo34hlxf</v>
@@ -2171,10 +2171,10 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L43" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M43" t="str">
         <v>msokwhmdho1q0</v>
@@ -2212,10 +2212,10 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L44" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M44" t="str">
         <v>msokwhmdegi75</v>
@@ -2253,10 +2253,10 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L45" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M45" t="str">
         <v>msokwhmdcolem</v>
@@ -2294,10 +2294,10 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L46" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M46" t="str">
         <v>msokwhmd3im81</v>
@@ -2335,10 +2335,10 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L47" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M47" t="str">
         <v>msokwhmdy3sam</v>
@@ -2376,10 +2376,10 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L48" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M48" t="str">
         <v>msokwhmdnrh8d</v>
@@ -2417,10 +2417,10 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L49" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M49" t="str">
         <v>msokwhmdjqudo</v>
@@ -2458,10 +2458,10 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L50" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M50" t="str">
         <v>msokwhmdew0dw</v>
@@ -2499,10 +2499,10 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L51" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M51" t="str">
         <v>msokwhmdul4ig</v>
@@ -2540,10 +2540,10 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L52" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M52" t="str">
         <v>msokwhmdgbas5</v>
@@ -2581,10 +2581,10 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L53" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M53" t="str">
         <v>msokxlxs06a9x</v>
@@ -2622,10 +2622,10 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L54" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M54" t="str">
         <v>msokxlxs42f77</v>
@@ -2663,10 +2663,10 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L55" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M55" t="str">
         <v>msokxlxs6xyeg</v>
@@ -2704,10 +2704,10 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L56" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M56" t="str">
         <v>msokxlxs7dltq</v>
@@ -2745,10 +2745,10 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L57" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M57" t="str">
         <v>msokxlxsgvc7b</v>
@@ -2786,10 +2786,10 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L58" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M58" t="str">
         <v>msokxlxsrox0v</v>
@@ -2827,10 +2827,10 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L59" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M59" t="str">
         <v>msokxlxsbwhdd</v>
@@ -2868,10 +2868,10 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L60" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M60" t="str">
         <v>msokxx7vw4unh</v>
@@ -2909,10 +2909,10 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L61" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M61" t="str">
         <v>msokxx7vcpo7d</v>
@@ -2950,10 +2950,10 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L62" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M62" t="str">
         <v>msokxx7vxd5a6</v>
@@ -2991,10 +2991,10 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L63" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M63" t="str">
         <v>msol0sqedwrwb</v>
@@ -3032,10 +3032,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L64" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M64" t="str">
         <v>msol0sqengvk7</v>
@@ -3073,10 +3073,10 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L65" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M65" t="str">
         <v>msol0sqeuws7d</v>
@@ -3114,10 +3114,10 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L66" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M66" t="str">
         <v>msol0sqekcfzc</v>
@@ -3155,10 +3155,10 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L67" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M67" t="str">
         <v>msol0sqemrzds</v>
@@ -3196,10 +3196,10 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L68" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M68" t="str">
         <v>msol0sqepq0ch</v>
@@ -3237,10 +3237,10 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L69" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M69" t="str">
         <v>msol0sqe12vt4</v>
@@ -3278,10 +3278,10 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L70" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M70" t="str">
         <v>msol0sqelotvw</v>
@@ -3319,10 +3319,10 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L71" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M71" t="str">
         <v>msol0sqe3ckax</v>
@@ -3360,10 +3360,10 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L72" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M72" t="str">
         <v>msol0sqe7neja</v>
@@ -3401,10 +3401,10 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L73" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M73" t="str">
         <v>msol0sqemccjp</v>
@@ -3442,10 +3442,10 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L74" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M74" t="str">
         <v>msol0sqei4fpl</v>
@@ -3483,10 +3483,10 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L75" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M75" t="str">
         <v>msol0sqe37ejp</v>
@@ -3524,10 +3524,10 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L76" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M76" t="str">
         <v>msol0sqe2tdno</v>
@@ -3565,10 +3565,10 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L77" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M77" t="str">
         <v>msol0sqe3wknl</v>
@@ -3606,10 +3606,10 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L78" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M78" t="str">
         <v>msol0sqejzchq</v>
@@ -3647,10 +3647,10 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L79" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M79" t="str">
         <v>msol0sqet2uhb</v>
@@ -3688,10 +3688,10 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L80" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M80" t="str">
         <v>msol0sqe5wsbz</v>
@@ -3729,10 +3729,10 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L81" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M81" t="str">
         <v>msol0sqezkuii</v>
@@ -3770,10 +3770,10 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L82" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M82" t="str">
         <v>msol0sqe4p67x</v>
@@ -3811,10 +3811,10 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L83" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M83" t="str">
         <v>msol0sqehxbfj</v>
@@ -3852,10 +3852,10 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L84" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M84" t="str">
         <v>msol0sqe6dg2v</v>
@@ -3893,10 +3893,10 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L85" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M85" t="str">
         <v>msol0sqewy04g</v>
@@ -3934,10 +3934,10 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L86" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M86" t="str">
         <v>msol0sqee580t</v>
@@ -3975,10 +3975,10 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L87" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M87" t="str">
         <v>msol0sqeiznyn</v>
@@ -4016,10 +4016,10 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L88" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M88" t="str">
         <v>msol0sqeohz5d</v>
@@ -4057,10 +4057,10 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L89" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M89" t="str">
         <v>msol0sqepq9bm</v>
@@ -4098,10 +4098,10 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L90" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M90" t="str">
         <v>msol0sqepn626</v>
@@ -4139,10 +4139,10 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L91" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M91" t="str">
         <v>msol0sqe28q4z</v>
@@ -4180,10 +4180,10 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L92" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M92" t="str">
         <v>msol0sqe56y72</v>
@@ -4221,10 +4221,10 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L93" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M93" t="str">
         <v>msol0sqeyukhl</v>
@@ -4262,10 +4262,10 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L94" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M94" t="str">
         <v>msol2k62oicjg</v>
@@ -4441,7 +4441,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -4535,7 +4535,7 @@
         <v>53%</v>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -4588,7 +4588,7 @@
         <v>35%</v>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -4641,7 +4641,7 @@
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -4694,7 +4694,7 @@
         <v>0%</v>
       </c>
       <c r="K5" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L5" t="str">
         <v>TRUE</v>
@@ -4747,7 +4747,7 @@
         <v>0%</v>
       </c>
       <c r="K6" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L6" t="str">
         <v>FALSE</v>
@@ -4800,7 +4800,7 @@
         <v>0%</v>
       </c>
       <c r="K7" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L7" t="str">
         <v>FALSE</v>
@@ -4841,7 +4841,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4909,7 +4909,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -4944,7 +4944,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -4979,7 +4979,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -5014,7 +5014,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -5049,7 +5049,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -5084,7 +5084,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -5127,7 +5127,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -5169,7 +5169,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -5220,7 +5220,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -5290,7 +5290,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -5325,7 +5325,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -5360,7 +5360,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -5395,7 +5395,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Sprints" sheetId="2" r:id="rId2"/>
     <sheet name="Epics" sheetId="3" r:id="rId3"/>
     <sheet name="Subtasks" sheetId="4" r:id="rId4"/>
+    <sheet name="Categories" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -5406,4 +5407,63 @@
     <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="43.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Color</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Epic IDs</v>
+      </c>
+      <c r="D1" t="str">
+        <v>__id</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Machine Learning</v>
+      </c>
+      <c r="B2" t="str">
+        <v>#7c5cd8</v>
+      </c>
+      <c r="C2" t="str">
+        <v>mskjl8cuwbnzs,mskjtuixm69sd,mskk074pigdwg</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mspj1gugclajb</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>RAG</v>
+      </c>
+      <c r="B3" t="str">
+        <v>#7c5cd8</v>
+      </c>
+      <c r="C3" t="str">
+        <v>msokv11v8pdah,msokz90zh9nmn,msol2au4dexr8</v>
+      </c>
+      <c r="D3" t="str">
+        <v>mspj1pbk2kkn9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -413,8 +413,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -491,10 +491,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -532,10 +532,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -573,10 +573,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -614,10 +614,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -655,10 +655,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -696,10 +696,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -737,10 +737,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -778,10 +778,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -819,10 +819,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -860,10 +860,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -901,10 +901,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -930,7 +930,7 @@
         <v>2026-08</v>
       </c>
       <c r="G13" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H13" t="str">
         <v>Low</v>
@@ -942,10 +942,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -983,10 +983,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1024,10 +1024,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1065,10 +1065,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1106,10 +1106,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1147,10 +1147,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1188,10 +1188,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1229,10 +1229,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1270,10 +1270,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1299,7 +1299,7 @@
         <v>2026-08</v>
       </c>
       <c r="G22" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H22" t="str">
         <v>Low</v>
@@ -1311,10 +1311,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1352,10 +1352,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1393,10 +1393,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1434,10 +1434,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1475,10 +1475,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1557,10 +1557,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1598,10 +1598,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1639,10 +1639,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1680,10 +1680,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1721,10 +1721,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1762,10 +1762,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1803,10 +1803,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1844,10 +1844,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1885,10 +1885,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1914,7 +1914,7 @@
         <v>2026-08</v>
       </c>
       <c r="G37" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H37" t="str">
         <v>Medium</v>
@@ -1926,10 +1926,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -1967,10 +1967,10 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L38" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M38" t="str">
         <v>msokvqo38bfww</v>
@@ -2008,10 +2008,10 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L39" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M39" t="str">
         <v>msokvqo3tpfld</v>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L40" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M40" t="str">
         <v>msokvqo323mt3</v>
@@ -2090,10 +2090,10 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L41" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M41" t="str">
         <v>msokvqo3fjm2f</v>
@@ -2131,10 +2131,10 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L42" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M42" t="str">
         <v>msokvqo34hlxf</v>
@@ -2172,10 +2172,10 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L43" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M43" t="str">
         <v>msokwhmdho1q0</v>
@@ -2213,10 +2213,10 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L44" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M44" t="str">
         <v>msokwhmdegi75</v>
@@ -2254,10 +2254,10 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L45" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M45" t="str">
         <v>msokwhmdcolem</v>
@@ -2295,10 +2295,10 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L46" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M46" t="str">
         <v>msokwhmd3im81</v>
@@ -2336,10 +2336,10 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L47" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M47" t="str">
         <v>msokwhmdy3sam</v>
@@ -2377,10 +2377,10 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L48" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M48" t="str">
         <v>msokwhmdnrh8d</v>
@@ -2418,10 +2418,10 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L49" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M49" t="str">
         <v>msokwhmdjqudo</v>
@@ -2459,10 +2459,10 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L50" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M50" t="str">
         <v>msokwhmdew0dw</v>
@@ -2500,10 +2500,10 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L51" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M51" t="str">
         <v>msokwhmdul4ig</v>
@@ -2541,10 +2541,10 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L52" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M52" t="str">
         <v>msokwhmdgbas5</v>
@@ -2582,10 +2582,10 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L53" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M53" t="str">
         <v>msokxlxs06a9x</v>
@@ -2623,10 +2623,10 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L54" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M54" t="str">
         <v>msokxlxs42f77</v>
@@ -2664,10 +2664,10 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L55" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M55" t="str">
         <v>msokxlxs6xyeg</v>
@@ -2705,10 +2705,10 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L56" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M56" t="str">
         <v>msokxlxs7dltq</v>
@@ -2746,10 +2746,10 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L57" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M57" t="str">
         <v>msokxlxsgvc7b</v>
@@ -2787,10 +2787,10 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L58" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M58" t="str">
         <v>msokxlxsrox0v</v>
@@ -2828,10 +2828,10 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L59" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M59" t="str">
         <v>msokxlxsbwhdd</v>
@@ -2869,10 +2869,10 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L60" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M60" t="str">
         <v>msokxx7vw4unh</v>
@@ -2910,10 +2910,10 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L61" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M61" t="str">
         <v>msokxx7vcpo7d</v>
@@ -2951,10 +2951,10 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L62" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M62" t="str">
         <v>msokxx7vxd5a6</v>
@@ -2980,7 +2980,7 @@
         <v>2026-08</v>
       </c>
       <c r="G63" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H63" t="str">
         <v>Medium</v>
@@ -2992,10 +2992,10 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L63" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M63" t="str">
         <v>msol0sqedwrwb</v>
@@ -3021,7 +3021,7 @@
         <v>2026-08</v>
       </c>
       <c r="G64" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H64" t="str">
         <v>Medium</v>
@@ -3033,10 +3033,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L64" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M64" t="str">
         <v>msol0sqengvk7</v>
@@ -3062,7 +3062,7 @@
         <v>2026-08</v>
       </c>
       <c r="G65" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H65" t="str">
         <v>Medium</v>
@@ -3074,10 +3074,10 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L65" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M65" t="str">
         <v>msol0sqeuws7d</v>
@@ -3103,7 +3103,7 @@
         <v>2026-08</v>
       </c>
       <c r="G66" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H66" t="str">
         <v>Medium</v>
@@ -3115,10 +3115,10 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L66" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M66" t="str">
         <v>msol0sqekcfzc</v>
@@ -3144,7 +3144,7 @@
         <v>2026-08</v>
       </c>
       <c r="G67" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H67" t="str">
         <v>Medium</v>
@@ -3156,10 +3156,10 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L67" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M67" t="str">
         <v>msol0sqemrzds</v>
@@ -3185,7 +3185,7 @@
         <v>2026-08</v>
       </c>
       <c r="G68" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H68" t="str">
         <v>Medium</v>
@@ -3197,10 +3197,10 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L68" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M68" t="str">
         <v>msol0sqepq0ch</v>
@@ -3226,7 +3226,7 @@
         <v>2026-08</v>
       </c>
       <c r="G69" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H69" t="str">
         <v>Medium</v>
@@ -3238,10 +3238,10 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L69" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M69" t="str">
         <v>msol0sqe12vt4</v>
@@ -3267,7 +3267,7 @@
         <v>2026-08</v>
       </c>
       <c r="G70" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H70" t="str">
         <v>Medium</v>
@@ -3279,10 +3279,10 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L70" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M70" t="str">
         <v>msol0sqelotvw</v>
@@ -3308,7 +3308,7 @@
         <v>2026-08</v>
       </c>
       <c r="G71" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H71" t="str">
         <v>Medium</v>
@@ -3320,10 +3320,10 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L71" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M71" t="str">
         <v>msol0sqe3ckax</v>
@@ -3349,7 +3349,7 @@
         <v>2026-08</v>
       </c>
       <c r="G72" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H72" t="str">
         <v>Medium</v>
@@ -3361,10 +3361,10 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L72" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M72" t="str">
         <v>msol0sqe7neja</v>
@@ -3390,7 +3390,7 @@
         <v>2026-08</v>
       </c>
       <c r="G73" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H73" t="str">
         <v>Medium</v>
@@ -3402,10 +3402,10 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L73" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M73" t="str">
         <v>msol0sqemccjp</v>
@@ -3431,7 +3431,7 @@
         <v>2026-08</v>
       </c>
       <c r="G74" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H74" t="str">
         <v>Medium</v>
@@ -3443,10 +3443,10 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L74" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M74" t="str">
         <v>msol0sqei4fpl</v>
@@ -3472,7 +3472,7 @@
         <v>2026-08</v>
       </c>
       <c r="G75" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H75" t="str">
         <v>Medium</v>
@@ -3484,10 +3484,10 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L75" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M75" t="str">
         <v>msol0sqe37ejp</v>
@@ -3513,7 +3513,7 @@
         <v>2026-08</v>
       </c>
       <c r="G76" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H76" t="str">
         <v>Medium</v>
@@ -3525,10 +3525,10 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L76" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M76" t="str">
         <v>msol0sqe2tdno</v>
@@ -3554,7 +3554,7 @@
         <v>2026-08</v>
       </c>
       <c r="G77" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H77" t="str">
         <v>Medium</v>
@@ -3566,10 +3566,10 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L77" t="str">
-        <v>Aug 11, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M77" t="str">
         <v>msol0sqe3wknl</v>
@@ -3607,10 +3607,10 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L78" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M78" t="str">
         <v>msol0sqejzchq</v>
@@ -3648,10 +3648,10 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L79" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M79" t="str">
         <v>msol0sqet2uhb</v>
@@ -3689,10 +3689,10 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L80" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M80" t="str">
         <v>msol0sqe5wsbz</v>
@@ -3730,10 +3730,10 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L81" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M81" t="str">
         <v>msol0sqezkuii</v>
@@ -3771,10 +3771,10 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L82" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M82" t="str">
         <v>msol0sqe4p67x</v>
@@ -3812,10 +3812,10 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L83" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M83" t="str">
         <v>msol0sqehxbfj</v>
@@ -3853,10 +3853,10 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L84" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M84" t="str">
         <v>msol0sqe6dg2v</v>
@@ -3894,10 +3894,10 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L85" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M85" t="str">
         <v>msol0sqewy04g</v>
@@ -3935,10 +3935,10 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L86" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M86" t="str">
         <v>msol0sqee580t</v>
@@ -3976,10 +3976,10 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L87" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M87" t="str">
         <v>msol0sqeiznyn</v>
@@ -4017,10 +4017,10 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L88" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M88" t="str">
         <v>msol0sqeohz5d</v>
@@ -4058,10 +4058,10 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L89" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M89" t="str">
         <v>msol0sqepq9bm</v>
@@ -4099,10 +4099,10 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L90" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M90" t="str">
         <v>msol0sqepn626</v>
@@ -4140,10 +4140,10 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L91" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M91" t="str">
         <v>msol0sqe28q4z</v>
@@ -4181,10 +4181,10 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L92" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M92" t="str">
         <v>msol0sqe56y72</v>
@@ -4222,10 +4222,10 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L93" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M93" t="str">
         <v>msol0sqeyukhl</v>
@@ -4263,10 +4263,10 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L94" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M94" t="str">
         <v>msol2k62oicjg</v>
@@ -4400,7 +4400,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4412,10 +4412,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>83%</v>
+        <v>100%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -4442,7 +4442,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -4518,7 +4518,7 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4530,13 +4530,13 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2" t="str">
-        <v>53%</v>
+        <v>60%</v>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -4571,7 +4571,7 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4583,13 +4583,13 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" t="str">
-        <v>35%</v>
+        <v>40%</v>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -4624,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4636,13 +4636,13 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="str">
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -4695,7 +4695,7 @@
         <v>0%</v>
       </c>
       <c r="K5" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L5" t="str">
         <v>TRUE</v>
@@ -4730,7 +4730,7 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4742,13 +4742,13 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J6" t="str">
-        <v>0%</v>
+        <v>48%</v>
       </c>
       <c r="K6" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L6" t="str">
         <v>FALSE</v>
@@ -4801,7 +4801,7 @@
         <v>0%</v>
       </c>
       <c r="K7" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L7" t="str">
         <v>FALSE</v>
@@ -4842,7 +4842,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4910,7 +4910,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -4945,7 +4945,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -4980,7 +4980,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -5015,7 +5015,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -5050,7 +5050,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -5085,7 +5085,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -5128,7 +5128,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -5170,7 +5170,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -5209,7 +5209,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F10" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G10" t="str">
         <v>Medium</v>
@@ -5221,7 +5221,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -5256,7 +5256,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -5291,7 +5291,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -5326,7 +5326,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -5396,7 +5396,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -401,11 +401,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M101"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
@@ -4272,9 +4272,296 @@
         <v>msol2k62oicjg</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Get started</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G95" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L95" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M95" t="str">
+        <v>msribdnoza7js</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Servers</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G96" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L96" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M96" t="str">
+        <v>msribdnogrvsu</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Inside your handler</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G97" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L97" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M97" t="str">
+        <v>msribdnote35t</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Running your server</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G98" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L98" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M98" t="str">
+        <v>msribdnomnby7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Clients</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G99" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L99" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M99" t="str">
+        <v>msribdnomwbz2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Advanced</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G100" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L100" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M100" t="str">
+        <v>msribdno4q8a4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>API Reference</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G101" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L101" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M101" t="str">
+        <v>msribdno3tqby</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M101"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4430,9 +4717,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
@@ -4822,9 +5109,62 @@
         <v>msol2au4dexr8</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>MCP Python SDK</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K8" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L8" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>msri9am8ug3yb</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5411,7 +5751,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -5461,9 +5801,23 @@
         <v>mspj1pbk2kkn9</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MCP</v>
+      </c>
+      <c r="B4" t="str">
+        <v>#138125</v>
+      </c>
+      <c r="C4" t="str">
+        <v>msri9am8ug3yb</v>
+      </c>
+      <c r="D4" t="str">
+        <v>msri8r0c3t2g3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -413,8 +413,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -491,10 +491,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -532,10 +532,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -573,10 +573,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -614,10 +614,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -655,10 +655,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -696,10 +696,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -737,10 +737,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -778,10 +778,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -819,10 +819,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -860,10 +860,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -901,10 +901,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -942,10 +942,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -983,10 +983,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1024,10 +1024,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1065,10 +1065,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1106,10 +1106,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1147,10 +1147,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1188,10 +1188,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1229,10 +1229,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1270,10 +1270,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1311,10 +1311,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1352,10 +1352,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1393,10 +1393,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1434,10 +1434,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1475,10 +1475,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1557,10 +1557,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1598,10 +1598,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1639,10 +1639,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1680,10 +1680,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1721,10 +1721,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1762,10 +1762,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1803,10 +1803,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1844,10 +1844,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1885,10 +1885,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1914,7 +1914,7 @@
         <v>2026-08</v>
       </c>
       <c r="G37" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H37" t="str">
         <v>Medium</v>
@@ -1926,10 +1926,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -1967,10 +1967,10 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L38" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M38" t="str">
         <v>msokvqo38bfww</v>
@@ -2008,10 +2008,10 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L39" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M39" t="str">
         <v>msokvqo3tpfld</v>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L40" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M40" t="str">
         <v>msokvqo323mt3</v>
@@ -2090,10 +2090,10 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L41" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M41" t="str">
         <v>msokvqo3fjm2f</v>
@@ -2131,10 +2131,10 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L42" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M42" t="str">
         <v>msokvqo34hlxf</v>
@@ -2172,10 +2172,10 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L43" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M43" t="str">
         <v>msokwhmdho1q0</v>
@@ -2213,10 +2213,10 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L44" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M44" t="str">
         <v>msokwhmdegi75</v>
@@ -2254,10 +2254,10 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L45" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M45" t="str">
         <v>msokwhmdcolem</v>
@@ -2295,10 +2295,10 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L46" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M46" t="str">
         <v>msokwhmd3im81</v>
@@ -2336,10 +2336,10 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L47" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M47" t="str">
         <v>msokwhmdy3sam</v>
@@ -2377,10 +2377,10 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L48" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M48" t="str">
         <v>msokwhmdnrh8d</v>
@@ -2418,10 +2418,10 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L49" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M49" t="str">
         <v>msokwhmdjqudo</v>
@@ -2459,10 +2459,10 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L50" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M50" t="str">
         <v>msokwhmdew0dw</v>
@@ -2500,10 +2500,10 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L51" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M51" t="str">
         <v>msokwhmdul4ig</v>
@@ -2541,10 +2541,10 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L52" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M52" t="str">
         <v>msokwhmdgbas5</v>
@@ -2582,10 +2582,10 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L53" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M53" t="str">
         <v>msokxlxs06a9x</v>
@@ -2623,10 +2623,10 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L54" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M54" t="str">
         <v>msokxlxs42f77</v>
@@ -2664,10 +2664,10 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L55" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M55" t="str">
         <v>msokxlxs6xyeg</v>
@@ -2705,10 +2705,10 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L56" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M56" t="str">
         <v>msokxlxs7dltq</v>
@@ -2746,10 +2746,10 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L57" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M57" t="str">
         <v>msokxlxsgvc7b</v>
@@ -2787,10 +2787,10 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L58" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M58" t="str">
         <v>msokxlxsrox0v</v>
@@ -2828,10 +2828,10 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L59" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M59" t="str">
         <v>msokxlxsbwhdd</v>
@@ -2869,10 +2869,10 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L60" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M60" t="str">
         <v>msokxx7vw4unh</v>
@@ -2910,10 +2910,10 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L61" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M61" t="str">
         <v>msokxx7vcpo7d</v>
@@ -2951,10 +2951,10 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L62" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M62" t="str">
         <v>msokxx7vxd5a6</v>
@@ -2992,10 +2992,10 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L63" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M63" t="str">
         <v>msol0sqedwrwb</v>
@@ -3033,10 +3033,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L64" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M64" t="str">
         <v>msol0sqengvk7</v>
@@ -3074,10 +3074,10 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L65" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M65" t="str">
         <v>msol0sqeuws7d</v>
@@ -3115,10 +3115,10 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L66" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M66" t="str">
         <v>msol0sqekcfzc</v>
@@ -3156,10 +3156,10 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L67" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M67" t="str">
         <v>msol0sqemrzds</v>
@@ -3197,10 +3197,10 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L68" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M68" t="str">
         <v>msol0sqepq0ch</v>
@@ -3238,10 +3238,10 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L69" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M69" t="str">
         <v>msol0sqe12vt4</v>
@@ -3279,10 +3279,10 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L70" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M70" t="str">
         <v>msol0sqelotvw</v>
@@ -3320,10 +3320,10 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L71" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M71" t="str">
         <v>msol0sqe3ckax</v>
@@ -3361,10 +3361,10 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L72" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M72" t="str">
         <v>msol0sqe7neja</v>
@@ -3402,10 +3402,10 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L73" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M73" t="str">
         <v>msol0sqemccjp</v>
@@ -3443,10 +3443,10 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L74" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M74" t="str">
         <v>msol0sqei4fpl</v>
@@ -3484,10 +3484,10 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L75" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M75" t="str">
         <v>msol0sqe37ejp</v>
@@ -3525,10 +3525,10 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L76" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M76" t="str">
         <v>msol0sqe2tdno</v>
@@ -3566,10 +3566,10 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L77" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M77" t="str">
         <v>msol0sqe3wknl</v>
@@ -3607,10 +3607,10 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L78" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M78" t="str">
         <v>msol0sqejzchq</v>
@@ -3648,10 +3648,10 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L79" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M79" t="str">
         <v>msol0sqet2uhb</v>
@@ -3689,10 +3689,10 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L80" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M80" t="str">
         <v>msol0sqe5wsbz</v>
@@ -3730,10 +3730,10 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L81" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M81" t="str">
         <v>msol0sqezkuii</v>
@@ -3771,10 +3771,10 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L82" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M82" t="str">
         <v>msol0sqe4p67x</v>
@@ -3812,10 +3812,10 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L83" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M83" t="str">
         <v>msol0sqehxbfj</v>
@@ -3853,10 +3853,10 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L84" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M84" t="str">
         <v>msol0sqe6dg2v</v>
@@ -3894,10 +3894,10 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L85" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M85" t="str">
         <v>msol0sqewy04g</v>
@@ -3935,10 +3935,10 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L86" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M86" t="str">
         <v>msol0sqee580t</v>
@@ -3976,10 +3976,10 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L87" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M87" t="str">
         <v>msol0sqeiznyn</v>
@@ -4017,10 +4017,10 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L88" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M88" t="str">
         <v>msol0sqeohz5d</v>
@@ -4058,10 +4058,10 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L89" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M89" t="str">
         <v>msol0sqepq9bm</v>
@@ -4099,10 +4099,10 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L90" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M90" t="str">
         <v>msol0sqepn626</v>
@@ -4140,10 +4140,10 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L91" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M91" t="str">
         <v>msol0sqe28q4z</v>
@@ -4181,10 +4181,10 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L92" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M92" t="str">
         <v>msol0sqe56y72</v>
@@ -4222,10 +4222,10 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L93" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M93" t="str">
         <v>msol0sqeyukhl</v>
@@ -4263,10 +4263,10 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L94" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M94" t="str">
         <v>msol2k62oicjg</v>
@@ -4304,10 +4304,10 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L95" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M95" t="str">
         <v>msribdnoza7js</v>
@@ -4345,10 +4345,10 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L96" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M96" t="str">
         <v>msribdnogrvsu</v>
@@ -4386,10 +4386,10 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L97" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M97" t="str">
         <v>msribdnote35t</v>
@@ -4427,10 +4427,10 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L98" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M98" t="str">
         <v>msribdnomnby7</v>
@@ -4468,10 +4468,10 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L99" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M99" t="str">
         <v>msribdnomwbz2</v>
@@ -4509,10 +4509,10 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L100" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M100" t="str">
         <v>msribdno4q8a4</v>
@@ -4550,10 +4550,10 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L101" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M101" t="str">
         <v>msribdno3tqby</v>
@@ -4687,7 +4687,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4699,10 +4699,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="str">
-        <v>100%</v>
+        <v>94%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -4717,7 +4717,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -4729,7 +4729,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -4823,7 +4823,7 @@
         <v>60%</v>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -4876,7 +4876,7 @@
         <v>40%</v>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -4911,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4923,13 +4923,13 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -4982,7 +4982,7 @@
         <v>0%</v>
       </c>
       <c r="K5" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L5" t="str">
         <v>TRUE</v>
@@ -5035,7 +5035,7 @@
         <v>48%</v>
       </c>
       <c r="K6" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L6" t="str">
         <v>FALSE</v>
@@ -5088,7 +5088,7 @@
         <v>0%</v>
       </c>
       <c r="K7" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L7" t="str">
         <v>FALSE</v>
@@ -5141,7 +5141,7 @@
         <v>0%</v>
       </c>
       <c r="K8" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L8" t="str">
         <v>FALSE</v>
@@ -5162,9 +5162,62 @@
         <v>msri9am8ug3yb</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Aug 13, 2026</v>
+      </c>
+      <c r="L9" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="O9" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>msrprx3yrm2my</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5182,7 +5235,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5250,7 +5303,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -5285,7 +5338,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -5320,7 +5373,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -5355,7 +5408,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -5390,7 +5443,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -5425,7 +5478,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -5456,7 +5509,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F8" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G8" t="str">
         <v>Medium</v>
@@ -5468,7 +5521,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -5498,7 +5551,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F9" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G9" t="str">
         <v>Medium</v>
@@ -5510,7 +5563,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -5549,7 +5602,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F10" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G10" t="str">
         <v>Medium</v>
@@ -5561,7 +5614,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -5596,7 +5649,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -5631,7 +5684,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -5666,7 +5719,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -5701,7 +5754,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -5736,7 +5789,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -401,10 +401,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M104"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="55.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
@@ -413,8 +413,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -491,10 +491,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -532,10 +532,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -573,10 +573,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -614,10 +614,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -655,10 +655,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -696,10 +696,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -737,10 +737,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -778,10 +778,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -819,10 +819,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -860,10 +860,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -901,10 +901,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -942,10 +942,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -983,10 +983,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1024,10 +1024,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1065,10 +1065,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1106,10 +1106,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1147,10 +1147,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1188,10 +1188,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1229,10 +1229,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1270,10 +1270,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1311,10 +1311,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1352,10 +1352,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1393,10 +1393,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1434,10 +1434,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1475,10 +1475,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1557,10 +1557,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1598,10 +1598,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1639,10 +1639,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1680,10 +1680,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1721,10 +1721,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1762,10 +1762,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1803,10 +1803,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1844,10 +1844,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1885,10 +1885,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1926,10 +1926,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -1967,10 +1967,10 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L38" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M38" t="str">
         <v>msokvqo38bfww</v>
@@ -2008,10 +2008,10 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L39" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M39" t="str">
         <v>msokvqo3tpfld</v>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L40" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M40" t="str">
         <v>msokvqo323mt3</v>
@@ -2090,10 +2090,10 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L41" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M41" t="str">
         <v>msokvqo3fjm2f</v>
@@ -2131,10 +2131,10 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L42" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M42" t="str">
         <v>msokvqo34hlxf</v>
@@ -2172,10 +2172,10 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L43" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M43" t="str">
         <v>msokwhmdho1q0</v>
@@ -2213,10 +2213,10 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L44" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M44" t="str">
         <v>msokwhmdegi75</v>
@@ -2254,10 +2254,10 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L45" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M45" t="str">
         <v>msokwhmdcolem</v>
@@ -2295,10 +2295,10 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L46" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M46" t="str">
         <v>msokwhmd3im81</v>
@@ -2336,10 +2336,10 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L47" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M47" t="str">
         <v>msokwhmdy3sam</v>
@@ -2377,10 +2377,10 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L48" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M48" t="str">
         <v>msokwhmdnrh8d</v>
@@ -2418,10 +2418,10 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L49" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M49" t="str">
         <v>msokwhmdjqudo</v>
@@ -2459,10 +2459,10 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L50" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M50" t="str">
         <v>msokwhmdew0dw</v>
@@ -2500,10 +2500,10 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L51" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M51" t="str">
         <v>msokwhmdul4ig</v>
@@ -2541,10 +2541,10 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L52" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M52" t="str">
         <v>msokwhmdgbas5</v>
@@ -2582,10 +2582,10 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L53" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M53" t="str">
         <v>msokxlxs06a9x</v>
@@ -2623,10 +2623,10 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L54" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M54" t="str">
         <v>msokxlxs42f77</v>
@@ -2664,10 +2664,10 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L55" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M55" t="str">
         <v>msokxlxs6xyeg</v>
@@ -2705,10 +2705,10 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L56" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M56" t="str">
         <v>msokxlxs7dltq</v>
@@ -2746,10 +2746,10 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L57" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M57" t="str">
         <v>msokxlxsgvc7b</v>
@@ -2787,10 +2787,10 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L58" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M58" t="str">
         <v>msokxlxsrox0v</v>
@@ -2828,10 +2828,10 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L59" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M59" t="str">
         <v>msokxlxsbwhdd</v>
@@ -2869,10 +2869,10 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L60" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M60" t="str">
         <v>msokxx7vw4unh</v>
@@ -2910,10 +2910,10 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L61" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M61" t="str">
         <v>msokxx7vcpo7d</v>
@@ -2951,10 +2951,10 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L62" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M62" t="str">
         <v>msokxx7vxd5a6</v>
@@ -2992,10 +2992,10 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L63" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M63" t="str">
         <v>msol0sqedwrwb</v>
@@ -3033,10 +3033,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L64" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M64" t="str">
         <v>msol0sqengvk7</v>
@@ -3074,10 +3074,10 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L65" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M65" t="str">
         <v>msol0sqeuws7d</v>
@@ -3115,10 +3115,10 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L66" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M66" t="str">
         <v>msol0sqekcfzc</v>
@@ -3156,10 +3156,10 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L67" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M67" t="str">
         <v>msol0sqemrzds</v>
@@ -3197,10 +3197,10 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L68" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M68" t="str">
         <v>msol0sqepq0ch</v>
@@ -3238,10 +3238,10 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L69" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M69" t="str">
         <v>msol0sqe12vt4</v>
@@ -3279,10 +3279,10 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L70" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M70" t="str">
         <v>msol0sqelotvw</v>
@@ -3320,10 +3320,10 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L71" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M71" t="str">
         <v>msol0sqe3ckax</v>
@@ -3361,10 +3361,10 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L72" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M72" t="str">
         <v>msol0sqe7neja</v>
@@ -3402,10 +3402,10 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L73" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M73" t="str">
         <v>msol0sqemccjp</v>
@@ -3443,10 +3443,10 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L74" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M74" t="str">
         <v>msol0sqei4fpl</v>
@@ -3484,10 +3484,10 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L75" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M75" t="str">
         <v>msol0sqe37ejp</v>
@@ -3525,10 +3525,10 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L76" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M76" t="str">
         <v>msol0sqe2tdno</v>
@@ -3566,10 +3566,10 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L77" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M77" t="str">
         <v>msol0sqe3wknl</v>
@@ -3607,10 +3607,10 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L78" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M78" t="str">
         <v>msol0sqejzchq</v>
@@ -3648,10 +3648,10 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L79" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M79" t="str">
         <v>msol0sqet2uhb</v>
@@ -3689,10 +3689,10 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L80" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M80" t="str">
         <v>msol0sqe5wsbz</v>
@@ -3730,10 +3730,10 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L81" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M81" t="str">
         <v>msol0sqezkuii</v>
@@ -3771,10 +3771,10 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L82" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M82" t="str">
         <v>msol0sqe4p67x</v>
@@ -3812,10 +3812,10 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L83" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M83" t="str">
         <v>msol0sqehxbfj</v>
@@ -3853,10 +3853,10 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L84" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M84" t="str">
         <v>msol0sqe6dg2v</v>
@@ -3894,10 +3894,10 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L85" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M85" t="str">
         <v>msol0sqewy04g</v>
@@ -3935,10 +3935,10 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L86" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M86" t="str">
         <v>msol0sqee580t</v>
@@ -3976,10 +3976,10 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L87" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M87" t="str">
         <v>msol0sqeiznyn</v>
@@ -4017,10 +4017,10 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L88" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M88" t="str">
         <v>msol0sqeohz5d</v>
@@ -4058,10 +4058,10 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L89" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M89" t="str">
         <v>msol0sqepq9bm</v>
@@ -4099,10 +4099,10 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L90" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M90" t="str">
         <v>msol0sqepn626</v>
@@ -4140,10 +4140,10 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L91" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M91" t="str">
         <v>msol0sqe28q4z</v>
@@ -4181,10 +4181,10 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L92" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M92" t="str">
         <v>msol0sqe56y72</v>
@@ -4222,10 +4222,10 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L93" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M93" t="str">
         <v>msol0sqeyukhl</v>
@@ -4263,10 +4263,10 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L94" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M94" t="str">
         <v>msol2k62oicjg</v>
@@ -4304,10 +4304,10 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L95" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M95" t="str">
         <v>msribdnoza7js</v>
@@ -4345,10 +4345,10 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L96" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M96" t="str">
         <v>msribdnogrvsu</v>
@@ -4386,10 +4386,10 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L97" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M97" t="str">
         <v>msribdnote35t</v>
@@ -4427,10 +4427,10 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L98" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M98" t="str">
         <v>msribdnomnby7</v>
@@ -4468,10 +4468,10 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L99" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M99" t="str">
         <v>msribdnomwbz2</v>
@@ -4509,10 +4509,10 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L100" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M100" t="str">
         <v>msribdno4q8a4</v>
@@ -4550,18 +4550,163 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L101" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M101" t="str">
         <v>msribdno3tqby</v>
       </c>
     </row>
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str">
+        <v>Must Know First</v>
+      </c>
+      <c r="B102" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `tf` (Core)
+- `tf.keras`
+- `tf.data`
+- `tf.estimator`</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G102" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L102" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M102" t="str">
+        <v>msrpyjubxmu32</v>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str">
+        <v>Learn Next</v>
+      </c>
+      <c r="B103" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `tf.math`
+- `tf.linalg`
+- `tf.io`
+- `tf.image`
+- `tf.strings`
+- `tf.random`
+- `tf.nn`
+- `tf.audio`
+- `tf.bitset`
+- `tf.debugging`
+- `tf.errors`</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G103" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L103" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M103" t="str">
+        <v>msrpyjub8lew4</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str">
+        <v>Explore Last</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `tf.distribute`
+- `tf.lite`
+- `tf.saved_model`
+- `tf.sparse`
+- `tf.ragged`
+- `tf.sets`
+- `tf.signal`
+- `tf.queue`
+- `tf.compat`
+- `tf.experimental`</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G104" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="L104" t="str">
+        <v>13 Aug 2026</v>
+      </c>
+      <c r="M104" t="str">
+        <v>msrpyjubl1s1o</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M104"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4729,7 +4874,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -4823,7 +4968,7 @@
         <v>60%</v>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -4876,7 +5021,7 @@
         <v>40%</v>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -4929,7 +5074,7 @@
         <v>0%</v>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -4982,7 +5127,7 @@
         <v>0%</v>
       </c>
       <c r="K5" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L5" t="str">
         <v>TRUE</v>
@@ -5035,7 +5180,7 @@
         <v>48%</v>
       </c>
       <c r="K6" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L6" t="str">
         <v>FALSE</v>
@@ -5088,7 +5233,7 @@
         <v>0%</v>
       </c>
       <c r="K7" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L7" t="str">
         <v>FALSE</v>
@@ -5141,7 +5286,7 @@
         <v>0%</v>
       </c>
       <c r="K8" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L8" t="str">
         <v>FALSE</v>
@@ -5173,7 +5318,7 @@
         <v>Medium</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5188,13 +5333,13 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="str">
         <v>0%</v>
       </c>
       <c r="K9" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L9" t="str">
         <v>FALSE</v>
@@ -5235,7 +5380,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5303,7 +5448,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -5338,7 +5483,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -5373,7 +5518,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -5408,7 +5553,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -5443,7 +5588,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -5478,7 +5623,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -5521,7 +5666,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -5563,7 +5708,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -5614,7 +5759,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -5649,7 +5794,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -5684,7 +5829,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -5719,7 +5864,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -5754,7 +5899,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -5789,7 +5934,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M105"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
@@ -1914,7 +1914,7 @@
         <v>2026-08</v>
       </c>
       <c r="G37" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H37" t="str">
         <v>Medium</v>
@@ -1929,7 +1929,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>13 Aug 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -4704,9 +4704,50 @@
         <v>msrpyjubl1s1o</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G105" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="L105" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="M105" t="str">
+        <v>msujqqctg5pu3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M105"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4832,7 +4873,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4844,10 +4885,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>94%</v>
+        <v>100%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -4862,9 +4903,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
@@ -5053,10 +5094,10 @@
         <v>Medium</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5071,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="str">
-        <v>0%</v>
+        <v>50%</v>
       </c>
       <c r="K4" t="str">
         <v>8 Aug 2026</v>
@@ -5136,10 +5177,10 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>08:00</v>
+        <v>16:00</v>
       </c>
       <c r="O5" t="str">
-        <v>10:00</v>
+        <v>18:00</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -5360,16 +5401,69 @@
         <v>msrprx3yrm2my</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>RAG_PRACTICE_PROJECT</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K10" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="L10" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="O10" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>msuk6qp8zwkp3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K30"/>
   <cols>
     <col min="1" max="1" width="54.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
@@ -5654,7 +5748,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F8" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G8" t="str">
         <v>Medium</v>
@@ -5696,7 +5790,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F9" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G9" t="str">
         <v>Medium</v>
@@ -5747,7 +5841,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F10" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G10" t="str">
         <v>Medium</v>
@@ -5940,9 +6034,534 @@
         <v>msmndu14o94q4</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>1. Supervised learning</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K16" t="str">
+        <v>msujrugr9kf7c</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2. Unsupervised learning</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K17" t="str">
+        <v>msujs3ezrjisd</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3. Model selection and evaluation</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K18" t="str">
+        <v>msujsdx80sust</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>4. Metadata Routing</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K19" t="str">
+        <v>msujwakj566af</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>5. Inspection</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K20" t="str">
+        <v>msujwhc2tj26f</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>6. Visualizations</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K21" t="str">
+        <v>msujwnnd7mozo</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>7. Callbacks</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K22" t="str">
+        <v>msujwti0bvxmi</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>8. Dataset transformations</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K23" t="str">
+        <v>msujwznrrjplj</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>9. Dataset loading utilities</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K24" t="str">
+        <v>msujxcfxhbm9s</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>10. Computing with scikit-learn</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K25" t="str">
+        <v>msujximm4dgax</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>11. Model persistence</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K26" t="str">
+        <v>msujy9j4854th</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>12. Common pitfalls and recommended practices</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K27" t="str">
+        <v>msujyhn99tdy8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>13. Data Interoperability</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K28" t="str">
+        <v>msujynvc2jnuk</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>14. Choosing the right estimator</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K29" t="str">
+        <v>msujyurxkz61l</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>15. External Resources, Videos and Talks</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K30" t="str">
+        <v>msujz10gszpqf</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5953,7 +6572,7 @@
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="43.83203125" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5979,7 +6598,7 @@
         <v>#7c5cd8</v>
       </c>
       <c r="C2" t="str">
-        <v>mskjl8cuwbnzs,mskjtuixm69sd,mskk074pigdwg</v>
+        <v>mskjl8cuwbnzs,mskjtuixm69sd,mskk074pigdwg,msrprx3yrm2my</v>
       </c>
       <c r="D2" t="str">
         <v>mspj1gugclajb</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M113"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
@@ -4745,9 +4745,337 @@
         <v>msujqqctg5pu3</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Get Started</v>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G106" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L106" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M106" t="str">
+        <v>msv6eldtxyz5z</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Guides</v>
+      </c>
+      <c r="B107" t="str">
+        <v/>
+      </c>
+      <c r="C107" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G107" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L107" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M107" t="str">
+        <v>msv6eldt79wmb</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Core Concepts</v>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G108" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L108" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M108" t="str">
+        <v>msv6eldt2w2bn</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>MCP Integration</v>
+      </c>
+      <c r="B109" t="str">
+        <v/>
+      </c>
+      <c r="C109" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G109" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L109" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M109" t="str">
+        <v>msv6eldt8al3c</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Tools</v>
+      </c>
+      <c r="B110" t="str">
+        <v/>
+      </c>
+      <c r="C110" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G110" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L110" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M110" t="str">
+        <v>msv6eldt2io8e</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="B111" t="str">
+        <v/>
+      </c>
+      <c r="C111" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G111" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L111" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M111" t="str">
+        <v>msv6eldt8sk8w</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Learn</v>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G112" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L112" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M112" t="str">
+        <v>msv6eldtb3gi0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G113" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L113" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="M113" t="str">
+        <v>msv6eldtftuex</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M113"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4903,7 +5231,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -5454,9 +5782,62 @@
         <v>msuk6qp8zwkp3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CrewAI</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K11" t="str">
+        <v>16 Aug 2026</v>
+      </c>
+      <c r="L11" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v>msv6comjfd2xw</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q11"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M114"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
@@ -409,12 +409,12 @@
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -491,10 +491,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -532,10 +532,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -573,10 +573,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -614,10 +614,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -655,10 +655,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -696,10 +696,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -737,10 +737,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -778,10 +778,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -819,10 +819,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -860,10 +860,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -901,10 +901,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -942,10 +942,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -983,10 +983,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1024,10 +1024,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1065,10 +1065,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1106,10 +1106,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1147,10 +1147,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1188,10 +1188,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1229,10 +1229,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1270,10 +1270,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1311,10 +1311,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1352,10 +1352,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1393,10 +1393,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1434,10 +1434,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1475,10 +1475,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1557,10 +1557,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1598,10 +1598,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1639,10 +1639,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1680,10 +1680,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1721,10 +1721,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1762,10 +1762,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1803,10 +1803,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1844,10 +1844,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1885,10 +1885,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1926,10 +1926,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -1955,7 +1955,7 @@
         <v>2026-08</v>
       </c>
       <c r="G38" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H38" t="str">
         <v>Medium</v>
@@ -1967,10 +1967,10 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L38" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M38" t="str">
         <v>msokvqo38bfww</v>
@@ -1996,7 +1996,7 @@
         <v>2026-08</v>
       </c>
       <c r="G39" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H39" t="str">
         <v>Medium</v>
@@ -2008,10 +2008,10 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L39" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M39" t="str">
         <v>msokvqo3tpfld</v>
@@ -2037,7 +2037,7 @@
         <v>2026-08</v>
       </c>
       <c r="G40" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H40" t="str">
         <v>Medium</v>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L40" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M40" t="str">
         <v>msokvqo323mt3</v>
@@ -2078,7 +2078,7 @@
         <v>2026-08</v>
       </c>
       <c r="G41" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H41" t="str">
         <v>Medium</v>
@@ -2090,10 +2090,10 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L41" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M41" t="str">
         <v>msokvqo3fjm2f</v>
@@ -2119,7 +2119,7 @@
         <v>2026-08</v>
       </c>
       <c r="G42" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H42" t="str">
         <v>Medium</v>
@@ -2131,10 +2131,10 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L42" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M42" t="str">
         <v>msokvqo34hlxf</v>
@@ -2160,7 +2160,7 @@
         <v>2026-08</v>
       </c>
       <c r="G43" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H43" t="str">
         <v>Medium</v>
@@ -2172,10 +2172,10 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L43" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M43" t="str">
         <v>msokwhmdho1q0</v>
@@ -2201,7 +2201,7 @@
         <v>2026-08</v>
       </c>
       <c r="G44" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H44" t="str">
         <v>Medium</v>
@@ -2213,10 +2213,10 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L44" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M44" t="str">
         <v>msokwhmdegi75</v>
@@ -2242,7 +2242,7 @@
         <v>2026-08</v>
       </c>
       <c r="G45" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H45" t="str">
         <v>Medium</v>
@@ -2254,10 +2254,10 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L45" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M45" t="str">
         <v>msokwhmdcolem</v>
@@ -2283,7 +2283,7 @@
         <v>2026-08</v>
       </c>
       <c r="G46" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H46" t="str">
         <v>Medium</v>
@@ -2295,10 +2295,10 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L46" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M46" t="str">
         <v>msokwhmd3im81</v>
@@ -2324,7 +2324,7 @@
         <v>2026-08</v>
       </c>
       <c r="G47" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H47" t="str">
         <v>Medium</v>
@@ -2336,10 +2336,10 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L47" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M47" t="str">
         <v>msokwhmdy3sam</v>
@@ -2365,7 +2365,7 @@
         <v>2026-08</v>
       </c>
       <c r="G48" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H48" t="str">
         <v>Medium</v>
@@ -2377,10 +2377,10 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L48" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M48" t="str">
         <v>msokwhmdnrh8d</v>
@@ -2406,7 +2406,7 @@
         <v>2026-08</v>
       </c>
       <c r="G49" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H49" t="str">
         <v>Medium</v>
@@ -2418,10 +2418,10 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L49" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M49" t="str">
         <v>msokwhmdjqudo</v>
@@ -2447,7 +2447,7 @@
         <v>2026-08</v>
       </c>
       <c r="G50" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H50" t="str">
         <v>Medium</v>
@@ -2459,10 +2459,10 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L50" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M50" t="str">
         <v>msokwhmdew0dw</v>
@@ -2488,7 +2488,7 @@
         <v>2026-08</v>
       </c>
       <c r="G51" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H51" t="str">
         <v>Medium</v>
@@ -2500,10 +2500,10 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L51" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M51" t="str">
         <v>msokwhmdul4ig</v>
@@ -2529,7 +2529,7 @@
         <v>2026-08</v>
       </c>
       <c r="G52" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H52" t="str">
         <v>Medium</v>
@@ -2541,10 +2541,10 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L52" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M52" t="str">
         <v>msokwhmdgbas5</v>
@@ -2582,10 +2582,10 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L53" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M53" t="str">
         <v>msokxlxs06a9x</v>
@@ -2623,10 +2623,10 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L54" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M54" t="str">
         <v>msokxlxs42f77</v>
@@ -2664,10 +2664,10 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L55" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M55" t="str">
         <v>msokxlxs6xyeg</v>
@@ -2705,10 +2705,10 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L56" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M56" t="str">
         <v>msokxlxs7dltq</v>
@@ -2746,10 +2746,10 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L57" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M57" t="str">
         <v>msokxlxsgvc7b</v>
@@ -2787,10 +2787,10 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L58" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M58" t="str">
         <v>msokxlxsrox0v</v>
@@ -2828,10 +2828,10 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L59" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M59" t="str">
         <v>msokxlxsbwhdd</v>
@@ -2869,10 +2869,10 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L60" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M60" t="str">
         <v>msokxx7vw4unh</v>
@@ -2910,10 +2910,10 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L61" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M61" t="str">
         <v>msokxx7vcpo7d</v>
@@ -2951,10 +2951,10 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L62" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M62" t="str">
         <v>msokxx7vxd5a6</v>
@@ -2992,10 +2992,10 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L63" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M63" t="str">
         <v>msol0sqedwrwb</v>
@@ -3033,10 +3033,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L64" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M64" t="str">
         <v>msol0sqengvk7</v>
@@ -3074,10 +3074,10 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L65" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M65" t="str">
         <v>msol0sqeuws7d</v>
@@ -3115,10 +3115,10 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L66" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M66" t="str">
         <v>msol0sqekcfzc</v>
@@ -3156,10 +3156,10 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L67" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M67" t="str">
         <v>msol0sqemrzds</v>
@@ -3197,10 +3197,10 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L68" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M68" t="str">
         <v>msol0sqepq0ch</v>
@@ -3238,10 +3238,10 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L69" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M69" t="str">
         <v>msol0sqe12vt4</v>
@@ -3279,10 +3279,10 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L70" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M70" t="str">
         <v>msol0sqelotvw</v>
@@ -3320,10 +3320,10 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L71" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M71" t="str">
         <v>msol0sqe3ckax</v>
@@ -3361,10 +3361,10 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L72" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M72" t="str">
         <v>msol0sqe7neja</v>
@@ -3402,10 +3402,10 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L73" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M73" t="str">
         <v>msol0sqemccjp</v>
@@ -3443,10 +3443,10 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L74" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M74" t="str">
         <v>msol0sqei4fpl</v>
@@ -3484,10 +3484,10 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L75" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M75" t="str">
         <v>msol0sqe37ejp</v>
@@ -3525,10 +3525,10 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L76" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M76" t="str">
         <v>msol0sqe2tdno</v>
@@ -3566,10 +3566,10 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L77" t="str">
-        <v>12 Aug 2026</v>
+        <v>Aug 12, 2026</v>
       </c>
       <c r="M77" t="str">
         <v>msol0sqe3wknl</v>
@@ -3607,10 +3607,10 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L78" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M78" t="str">
         <v>msol0sqejzchq</v>
@@ -3648,10 +3648,10 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L79" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M79" t="str">
         <v>msol0sqet2uhb</v>
@@ -3689,10 +3689,10 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L80" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M80" t="str">
         <v>msol0sqe5wsbz</v>
@@ -3730,10 +3730,10 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L81" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M81" t="str">
         <v>msol0sqezkuii</v>
@@ -3771,10 +3771,10 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L82" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M82" t="str">
         <v>msol0sqe4p67x</v>
@@ -3812,10 +3812,10 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L83" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M83" t="str">
         <v>msol0sqehxbfj</v>
@@ -3853,10 +3853,10 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L84" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M84" t="str">
         <v>msol0sqe6dg2v</v>
@@ -3894,10 +3894,10 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L85" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M85" t="str">
         <v>msol0sqewy04g</v>
@@ -3935,10 +3935,10 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L86" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M86" t="str">
         <v>msol0sqee580t</v>
@@ -3976,10 +3976,10 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L87" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M87" t="str">
         <v>msol0sqeiznyn</v>
@@ -4017,10 +4017,10 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L88" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M88" t="str">
         <v>msol0sqeohz5d</v>
@@ -4058,10 +4058,10 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L89" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M89" t="str">
         <v>msol0sqepq9bm</v>
@@ -4099,10 +4099,10 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L90" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M90" t="str">
         <v>msol0sqepn626</v>
@@ -4140,10 +4140,10 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L91" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M91" t="str">
         <v>msol0sqe28q4z</v>
@@ -4181,10 +4181,10 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L92" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M92" t="str">
         <v>msol0sqe56y72</v>
@@ -4222,10 +4222,10 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L93" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M93" t="str">
         <v>msol0sqeyukhl</v>
@@ -4263,10 +4263,10 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L94" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="M94" t="str">
         <v>msol2k62oicjg</v>
@@ -4304,10 +4304,10 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L95" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M95" t="str">
         <v>msribdnoza7js</v>
@@ -4345,10 +4345,10 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L96" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M96" t="str">
         <v>msribdnogrvsu</v>
@@ -4386,10 +4386,10 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L97" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M97" t="str">
         <v>msribdnote35t</v>
@@ -4427,10 +4427,10 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L98" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M98" t="str">
         <v>msribdnomnby7</v>
@@ -4468,10 +4468,10 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L99" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M99" t="str">
         <v>msribdnomwbz2</v>
@@ -4509,10 +4509,10 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L100" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M100" t="str">
         <v>msribdno4q8a4</v>
@@ -4550,10 +4550,10 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L101" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M101" t="str">
         <v>msribdno3tqby</v>
@@ -4582,7 +4582,7 @@
         <v>2026-08</v>
       </c>
       <c r="G102" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H102" t="str">
         <v>Medium</v>
@@ -4594,10 +4594,10 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L102" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 17, 2026</v>
       </c>
       <c r="M102" t="str">
         <v>msrpyjubxmu32</v>
@@ -4645,10 +4645,10 @@
         <v/>
       </c>
       <c r="K103" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L103" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M103" t="str">
         <v>msrpyjub8lew4</v>
@@ -4695,10 +4695,10 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L104" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="M104" t="str">
         <v>msrpyjubl1s1o</v>
@@ -4736,10 +4736,10 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="L105" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="M105" t="str">
         <v>msujqqctg5pu3</v>
@@ -4765,7 +4765,7 @@
         <v>2026-08</v>
       </c>
       <c r="G106" t="str">
-        <v>To Do</v>
+        <v>In Progress</v>
       </c>
       <c r="H106" t="str">
         <v>Medium</v>
@@ -4777,10 +4777,10 @@
         <v/>
       </c>
       <c r="K106" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L106" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M106" t="str">
         <v>msv6eldtxyz5z</v>
@@ -4818,10 +4818,10 @@
         <v/>
       </c>
       <c r="K107" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L107" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M107" t="str">
         <v>msv6eldt79wmb</v>
@@ -4859,10 +4859,10 @@
         <v/>
       </c>
       <c r="K108" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L108" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M108" t="str">
         <v>msv6eldt2w2bn</v>
@@ -4900,10 +4900,10 @@
         <v/>
       </c>
       <c r="K109" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L109" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M109" t="str">
         <v>msv6eldt8al3c</v>
@@ -4941,10 +4941,10 @@
         <v/>
       </c>
       <c r="K110" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L110" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M110" t="str">
         <v>msv6eldt2io8e</v>
@@ -4982,10 +4982,10 @@
         <v/>
       </c>
       <c r="K111" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L111" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M111" t="str">
         <v>msv6eldt8sk8w</v>
@@ -5023,10 +5023,10 @@
         <v/>
       </c>
       <c r="K112" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L112" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M112" t="str">
         <v>msv6eldtb3gi0</v>
@@ -5064,18 +5064,59 @@
         <v/>
       </c>
       <c r="K113" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L113" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="M113" t="str">
         <v>msv6eldtftuex</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="B114" t="str">
+        <v/>
+      </c>
+      <c r="C114" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="G114" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="L114" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="M114" t="str">
+        <v>mswlrjq1miq5h</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M114"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5243,7 +5284,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -5337,7 +5378,7 @@
         <v>60%</v>
       </c>
       <c r="K2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -5390,7 +5431,7 @@
         <v>40%</v>
       </c>
       <c r="K3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -5443,7 +5484,7 @@
         <v>50%</v>
       </c>
       <c r="K4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -5478,7 +5519,7 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -5490,13 +5531,13 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J5" t="str">
-        <v>0%</v>
+        <v>60%</v>
       </c>
       <c r="K5" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L5" t="str">
         <v>TRUE</v>
@@ -5549,7 +5590,7 @@
         <v>48%</v>
       </c>
       <c r="K6" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L6" t="str">
         <v>FALSE</v>
@@ -5602,7 +5643,7 @@
         <v>0%</v>
       </c>
       <c r="K7" t="str">
-        <v>11 Aug 2026</v>
+        <v>Aug 11, 2026</v>
       </c>
       <c r="L7" t="str">
         <v>FALSE</v>
@@ -5655,7 +5696,7 @@
         <v>0%</v>
       </c>
       <c r="K8" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L8" t="str">
         <v>FALSE</v>
@@ -5687,10 +5728,10 @@
         <v>Medium</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -5705,10 +5746,10 @@
         <v>3</v>
       </c>
       <c r="J9" t="str">
-        <v>0%</v>
+        <v>25%</v>
       </c>
       <c r="K9" t="str">
-        <v>13 Aug 2026</v>
+        <v>Aug 13, 2026</v>
       </c>
       <c r="L9" t="str">
         <v>FALSE</v>
@@ -5761,7 +5802,7 @@
         <v>0%</v>
       </c>
       <c r="K10" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="L10" t="str">
         <v>FALSE</v>
@@ -5799,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -5808,13 +5849,13 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="str">
         <v>0%</v>
       </c>
       <c r="K11" t="str">
-        <v>16 Aug 2026</v>
+        <v>Aug 16, 2026</v>
       </c>
       <c r="L11" t="str">
         <v>FALSE</v>
@@ -5844,7 +5885,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K42"/>
   <cols>
     <col min="1" max="1" width="54.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
@@ -5855,7 +5896,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5923,7 +5964,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -5958,7 +5999,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -5993,7 +6034,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -6028,7 +6069,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -6063,7 +6104,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -6098,7 +6139,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -6141,7 +6182,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -6183,7 +6224,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -6234,7 +6275,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>8 Aug 2026</v>
+        <v>Aug 8, 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -6269,7 +6310,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -6304,7 +6345,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -6339,7 +6380,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -6374,7 +6415,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -6409,7 +6450,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>10 Aug 2026</v>
+        <v>Aug 10, 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>
@@ -6444,7 +6485,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K16" t="str">
         <v>msujrugr9kf7c</v>
@@ -6467,7 +6508,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G17" t="str">
         <v>Medium</v>
@@ -6479,7 +6520,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K17" t="str">
         <v>msujs3ezrjisd</v>
@@ -6514,7 +6555,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K18" t="str">
         <v>msujsdx80sust</v>
@@ -6549,7 +6590,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K19" t="str">
         <v>msujwakj566af</v>
@@ -6584,7 +6625,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K20" t="str">
         <v>msujwhc2tj26f</v>
@@ -6619,7 +6660,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K21" t="str">
         <v>msujwnnd7mozo</v>
@@ -6654,7 +6695,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K22" t="str">
         <v>msujwti0bvxmi</v>
@@ -6689,7 +6730,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K23" t="str">
         <v>msujwznrrjplj</v>
@@ -6724,7 +6765,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K24" t="str">
         <v>msujxcfxhbm9s</v>
@@ -6759,7 +6800,7 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K25" t="str">
         <v>msujximm4dgax</v>
@@ -6794,7 +6835,7 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K26" t="str">
         <v>msujy9j4854th</v>
@@ -6829,7 +6870,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K27" t="str">
         <v>msujyhn99tdy8</v>
@@ -6864,7 +6905,7 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K28" t="str">
         <v>msujynvc2jnuk</v>
@@ -6899,7 +6940,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K29" t="str">
         <v>msujyurxkz61l</v>
@@ -6934,22 +6975,442 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>15 Aug 2026</v>
+        <v>Aug 15, 2026</v>
       </c>
       <c r="K30" t="str">
         <v>msujz10gszpqf</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Tensorflow basics</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>Done</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K31" t="str">
+        <v>mswlsudlx8ecn</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Keras</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K32" t="str">
+        <v>mswlt75tei83v</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Build with Core</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K33" t="str">
+        <v>mswltlzdr47og</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Tensorflow in depth</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K34" t="str">
+        <v>mswltz96spp72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Customization</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K35" t="str">
+        <v>mswlubvt03mvt</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Data input pipelines</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K36" t="str">
+        <v>mswlumpdqog9b</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Import and export</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K37" t="str">
+        <v>mswluuchr3p6c</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Accelerators</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K38" t="str">
+        <v>mswlv4aq2qbbw</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K39" t="str">
+        <v>mswlvcnl0yz0v</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Model Garden</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K40" t="str">
+        <v>mswlvpdtxupgm</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Estimators</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K41" t="str">
+        <v>mswlvv0zpgcop</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Appendix</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v>Aug 17, 2026</v>
+      </c>
+      <c r="K42" t="str">
+        <v>mswlw58xtbs6m</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K42"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -7013,9 +7474,23 @@
         <v>msri8r0c3t2g3</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AI Agent</v>
+      </c>
+      <c r="B5" t="str">
+        <v>#7c5cd8</v>
+      </c>
+      <c r="C5" t="str">
+        <v>msv6comjfd2xw</v>
+      </c>
+      <c r="D5" t="str">
+        <v>msv6gtrcdc4s9</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -413,8 +413,8 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -479,7 +479,7 @@
         <v>2026-08</v>
       </c>
       <c r="G2" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H2" t="str">
         <v>Low</v>
@@ -491,10 +491,10 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M2" t="str">
         <v>mskjmm1ia28u3</v>
@@ -520,7 +520,7 @@
         <v>2026-08</v>
       </c>
       <c r="G3" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H3" t="str">
         <v>Low</v>
@@ -532,10 +532,10 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M3" t="str">
         <v>mskjmm1i9x9ut</v>
@@ -561,7 +561,7 @@
         <v>2026-08</v>
       </c>
       <c r="G4" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H4" t="str">
         <v>Low</v>
@@ -573,10 +573,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M4" t="str">
         <v>mskjmm1i0an4d</v>
@@ -602,7 +602,7 @@
         <v>2026-08</v>
       </c>
       <c r="G5" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H5" t="str">
         <v>Low</v>
@@ -614,10 +614,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L5" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M5" t="str">
         <v>mskjmm1ir8uys</v>
@@ -643,7 +643,7 @@
         <v>2026-08</v>
       </c>
       <c r="G6" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H6" t="str">
         <v>Low</v>
@@ -655,10 +655,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L6" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M6" t="str">
         <v>mskjmm1in1491</v>
@@ -684,7 +684,7 @@
         <v>2026-08</v>
       </c>
       <c r="G7" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H7" t="str">
         <v>Low</v>
@@ -696,10 +696,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L7" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M7" t="str">
         <v>mskjmm1iz5s6s</v>
@@ -725,7 +725,7 @@
         <v>2026-08</v>
       </c>
       <c r="G8" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H8" t="str">
         <v>Low</v>
@@ -737,10 +737,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L8" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M8" t="str">
         <v>mskjmm1iy83x2</v>
@@ -778,10 +778,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M9" t="str">
         <v>mskjmm1iahx06</v>
@@ -819,10 +819,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M10" t="str">
         <v>mskjmm1il6vzq</v>
@@ -860,10 +860,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L11" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M11" t="str">
         <v>mskjmm1idpwev</v>
@@ -901,10 +901,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L12" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M12" t="str">
         <v>mskjmm1irytor</v>
@@ -930,7 +930,7 @@
         <v>2026-08</v>
       </c>
       <c r="G13" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H13" t="str">
         <v>Low</v>
@@ -942,10 +942,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L13" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M13" t="str">
         <v>mskjmm1ijlwch</v>
@@ -971,7 +971,7 @@
         <v>2026-08</v>
       </c>
       <c r="G14" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H14" t="str">
         <v>Low</v>
@@ -983,10 +983,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M14" t="str">
         <v>mskjmm1izawzv</v>
@@ -1024,10 +1024,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L15" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M15" t="str">
         <v>mskjmm1i5vg3y</v>
@@ -1065,10 +1065,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L16" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M16" t="str">
         <v>mskjmm1ibeckq</v>
@@ -1094,7 +1094,7 @@
         <v>2026-08</v>
       </c>
       <c r="G17" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H17" t="str">
         <v>Low</v>
@@ -1106,10 +1106,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1135,7 +1135,7 @@
         <v>2026-08</v>
       </c>
       <c r="G18" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H18" t="str">
         <v>Low</v>
@@ -1147,10 +1147,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1176,7 +1176,7 @@
         <v>2026-08</v>
       </c>
       <c r="G19" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H19" t="str">
         <v>Low</v>
@@ -1188,10 +1188,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1217,7 +1217,7 @@
         <v>2026-08</v>
       </c>
       <c r="G20" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H20" t="str">
         <v>Low</v>
@@ -1229,10 +1229,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -1270,10 +1270,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L21" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M21" t="str">
         <v>mskjuazrh7x1j</v>
@@ -1299,7 +1299,7 @@
         <v>2026-08</v>
       </c>
       <c r="G22" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H22" t="str">
         <v>Low</v>
@@ -1311,10 +1311,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L22" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M22" t="str">
         <v>mskjuazrqr7t0</v>
@@ -1340,7 +1340,7 @@
         <v>2026-08</v>
       </c>
       <c r="G23" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H23" t="str">
         <v>Low</v>
@@ -1352,10 +1352,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L23" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M23" t="str">
         <v>mskjuazruu4xz</v>
@@ -1381,7 +1381,7 @@
         <v>2026-08</v>
       </c>
       <c r="G24" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H24" t="str">
         <v>Low</v>
@@ -1393,10 +1393,10 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L24" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M24" t="str">
         <v>mskjuazr7izui</v>
@@ -1422,7 +1422,7 @@
         <v>2026-08</v>
       </c>
       <c r="G25" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H25" t="str">
         <v>Low</v>
@@ -1434,10 +1434,10 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L25" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="M25" t="str">
         <v>mskjuazrk3kog</v>
@@ -1475,10 +1475,10 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L26" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M26" t="str">
         <v>mskjuazr76k5n</v>
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L27" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M27" t="str">
         <v>mskjuazrr55s1</v>
@@ -1557,10 +1557,10 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L28" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M28" t="str">
         <v>mskjuazr0gaye</v>
@@ -1598,10 +1598,10 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L29" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M29" t="str">
         <v>mskjuazrqqxe7</v>
@@ -1639,10 +1639,10 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L30" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M30" t="str">
         <v>mskjuazrf8qko</v>
@@ -1680,10 +1680,10 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L31" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M31" t="str">
         <v>mskjuazrhf6l1</v>
@@ -1721,10 +1721,10 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L32" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M32" t="str">
         <v>mskjuazr6y2w1</v>
@@ -1762,10 +1762,10 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L33" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M33" t="str">
         <v>mskjuazr1qa1k</v>
@@ -1803,10 +1803,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L34" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M34" t="str">
         <v>mskjuazrjvhms</v>
@@ -1844,10 +1844,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L35" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M35" t="str">
         <v>mskjuazrxonbt</v>
@@ -1885,10 +1885,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L36" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="M36" t="str">
         <v>mskjuazr4b0ct</v>
@@ -1926,10 +1926,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -1955,7 +1955,7 @@
         <v>2026-08</v>
       </c>
       <c r="G38" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H38" t="str">
         <v>Medium</v>
@@ -1967,10 +1967,10 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L38" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M38" t="str">
         <v>msokvqo38bfww</v>
@@ -1996,7 +1996,7 @@
         <v>2026-08</v>
       </c>
       <c r="G39" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H39" t="str">
         <v>Medium</v>
@@ -2008,10 +2008,10 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L39" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M39" t="str">
         <v>msokvqo3tpfld</v>
@@ -2037,7 +2037,7 @@
         <v>2026-08</v>
       </c>
       <c r="G40" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H40" t="str">
         <v>Medium</v>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L40" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M40" t="str">
         <v>msokvqo323mt3</v>
@@ -2078,7 +2078,7 @@
         <v>2026-08</v>
       </c>
       <c r="G41" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H41" t="str">
         <v>Medium</v>
@@ -2090,10 +2090,10 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L41" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M41" t="str">
         <v>msokvqo3fjm2f</v>
@@ -2119,7 +2119,7 @@
         <v>2026-08</v>
       </c>
       <c r="G42" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H42" t="str">
         <v>Medium</v>
@@ -2131,10 +2131,10 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L42" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M42" t="str">
         <v>msokvqo34hlxf</v>
@@ -2160,7 +2160,7 @@
         <v>2026-08</v>
       </c>
       <c r="G43" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H43" t="str">
         <v>Medium</v>
@@ -2172,10 +2172,10 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L43" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M43" t="str">
         <v>msokwhmdho1q0</v>
@@ -2201,7 +2201,7 @@
         <v>2026-08</v>
       </c>
       <c r="G44" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H44" t="str">
         <v>Medium</v>
@@ -2213,10 +2213,10 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L44" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M44" t="str">
         <v>msokwhmdegi75</v>
@@ -2242,7 +2242,7 @@
         <v>2026-08</v>
       </c>
       <c r="G45" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H45" t="str">
         <v>Medium</v>
@@ -2254,10 +2254,10 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L45" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M45" t="str">
         <v>msokwhmdcolem</v>
@@ -2283,7 +2283,7 @@
         <v>2026-08</v>
       </c>
       <c r="G46" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H46" t="str">
         <v>Medium</v>
@@ -2295,10 +2295,10 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L46" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M46" t="str">
         <v>msokwhmd3im81</v>
@@ -2324,7 +2324,7 @@
         <v>2026-08</v>
       </c>
       <c r="G47" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H47" t="str">
         <v>Medium</v>
@@ -2336,10 +2336,10 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L47" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M47" t="str">
         <v>msokwhmdy3sam</v>
@@ -2365,7 +2365,7 @@
         <v>2026-08</v>
       </c>
       <c r="G48" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H48" t="str">
         <v>Medium</v>
@@ -2377,10 +2377,10 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L48" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M48" t="str">
         <v>msokwhmdnrh8d</v>
@@ -2406,7 +2406,7 @@
         <v>2026-08</v>
       </c>
       <c r="G49" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H49" t="str">
         <v>Medium</v>
@@ -2418,10 +2418,10 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L49" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M49" t="str">
         <v>msokwhmdjqudo</v>
@@ -2447,7 +2447,7 @@
         <v>2026-08</v>
       </c>
       <c r="G50" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H50" t="str">
         <v>Medium</v>
@@ -2459,10 +2459,10 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L50" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M50" t="str">
         <v>msokwhmdew0dw</v>
@@ -2488,7 +2488,7 @@
         <v>2026-08</v>
       </c>
       <c r="G51" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H51" t="str">
         <v>Medium</v>
@@ -2500,10 +2500,10 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L51" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M51" t="str">
         <v>msokwhmdul4ig</v>
@@ -2529,7 +2529,7 @@
         <v>2026-08</v>
       </c>
       <c r="G52" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H52" t="str">
         <v>Medium</v>
@@ -2541,10 +2541,10 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L52" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M52" t="str">
         <v>msokwhmdgbas5</v>
@@ -2582,10 +2582,10 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L53" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M53" t="str">
         <v>msokxlxs06a9x</v>
@@ -2623,10 +2623,10 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L54" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M54" t="str">
         <v>msokxlxs42f77</v>
@@ -2664,10 +2664,10 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L55" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M55" t="str">
         <v>msokxlxs6xyeg</v>
@@ -2705,10 +2705,10 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L56" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M56" t="str">
         <v>msokxlxs7dltq</v>
@@ -2746,10 +2746,10 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L57" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M57" t="str">
         <v>msokxlxsgvc7b</v>
@@ -2787,10 +2787,10 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L58" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M58" t="str">
         <v>msokxlxsrox0v</v>
@@ -2828,10 +2828,10 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L59" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M59" t="str">
         <v>msokxlxsbwhdd</v>
@@ -2869,10 +2869,10 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L60" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M60" t="str">
         <v>msokxx7vw4unh</v>
@@ -2910,10 +2910,10 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L61" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M61" t="str">
         <v>msokxx7vcpo7d</v>
@@ -2951,10 +2951,10 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L62" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M62" t="str">
         <v>msokxx7vxd5a6</v>
@@ -2980,7 +2980,7 @@
         <v>2026-08</v>
       </c>
       <c r="G63" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H63" t="str">
         <v>Medium</v>
@@ -2992,10 +2992,10 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L63" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M63" t="str">
         <v>msol0sqedwrwb</v>
@@ -3021,7 +3021,7 @@
         <v>2026-08</v>
       </c>
       <c r="G64" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H64" t="str">
         <v>Medium</v>
@@ -3033,10 +3033,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L64" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M64" t="str">
         <v>msol0sqengvk7</v>
@@ -3062,7 +3062,7 @@
         <v>2026-08</v>
       </c>
       <c r="G65" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H65" t="str">
         <v>Medium</v>
@@ -3074,10 +3074,10 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L65" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M65" t="str">
         <v>msol0sqeuws7d</v>
@@ -3103,7 +3103,7 @@
         <v>2026-08</v>
       </c>
       <c r="G66" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H66" t="str">
         <v>Medium</v>
@@ -3115,10 +3115,10 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L66" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M66" t="str">
         <v>msol0sqekcfzc</v>
@@ -3144,7 +3144,7 @@
         <v>2026-08</v>
       </c>
       <c r="G67" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H67" t="str">
         <v>Medium</v>
@@ -3156,10 +3156,10 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L67" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M67" t="str">
         <v>msol0sqemrzds</v>
@@ -3185,7 +3185,7 @@
         <v>2026-08</v>
       </c>
       <c r="G68" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H68" t="str">
         <v>Medium</v>
@@ -3197,10 +3197,10 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L68" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M68" t="str">
         <v>msol0sqepq0ch</v>
@@ -3226,7 +3226,7 @@
         <v>2026-08</v>
       </c>
       <c r="G69" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H69" t="str">
         <v>Medium</v>
@@ -3238,10 +3238,10 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L69" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M69" t="str">
         <v>msol0sqe12vt4</v>
@@ -3267,7 +3267,7 @@
         <v>2026-08</v>
       </c>
       <c r="G70" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H70" t="str">
         <v>Medium</v>
@@ -3279,10 +3279,10 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L70" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M70" t="str">
         <v>msol0sqelotvw</v>
@@ -3308,7 +3308,7 @@
         <v>2026-08</v>
       </c>
       <c r="G71" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H71" t="str">
         <v>Medium</v>
@@ -3320,10 +3320,10 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L71" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M71" t="str">
         <v>msol0sqe3ckax</v>
@@ -3349,7 +3349,7 @@
         <v>2026-08</v>
       </c>
       <c r="G72" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H72" t="str">
         <v>Medium</v>
@@ -3361,10 +3361,10 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L72" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M72" t="str">
         <v>msol0sqe7neja</v>
@@ -3390,7 +3390,7 @@
         <v>2026-08</v>
       </c>
       <c r="G73" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H73" t="str">
         <v>Medium</v>
@@ -3402,10 +3402,10 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L73" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M73" t="str">
         <v>msol0sqemccjp</v>
@@ -3431,7 +3431,7 @@
         <v>2026-08</v>
       </c>
       <c r="G74" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H74" t="str">
         <v>Medium</v>
@@ -3443,10 +3443,10 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L74" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M74" t="str">
         <v>msol0sqei4fpl</v>
@@ -3472,7 +3472,7 @@
         <v>2026-08</v>
       </c>
       <c r="G75" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H75" t="str">
         <v>Medium</v>
@@ -3484,10 +3484,10 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L75" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M75" t="str">
         <v>msol0sqe37ejp</v>
@@ -3513,7 +3513,7 @@
         <v>2026-08</v>
       </c>
       <c r="G76" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H76" t="str">
         <v>Medium</v>
@@ -3525,10 +3525,10 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L76" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M76" t="str">
         <v>msol0sqe2tdno</v>
@@ -3554,7 +3554,7 @@
         <v>2026-08</v>
       </c>
       <c r="G77" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H77" t="str">
         <v>Medium</v>
@@ -3566,10 +3566,10 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L77" t="str">
-        <v>Aug 12, 2026</v>
+        <v>12 Aug 2026</v>
       </c>
       <c r="M77" t="str">
         <v>msol0sqe3wknl</v>
@@ -3607,10 +3607,10 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L78" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M78" t="str">
         <v>msol0sqejzchq</v>
@@ -3648,10 +3648,10 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L79" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M79" t="str">
         <v>msol0sqet2uhb</v>
@@ -3689,10 +3689,10 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L80" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M80" t="str">
         <v>msol0sqe5wsbz</v>
@@ -3730,10 +3730,10 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L81" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M81" t="str">
         <v>msol0sqezkuii</v>
@@ -3771,10 +3771,10 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L82" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M82" t="str">
         <v>msol0sqe4p67x</v>
@@ -3812,10 +3812,10 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L83" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M83" t="str">
         <v>msol0sqehxbfj</v>
@@ -3853,10 +3853,10 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L84" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M84" t="str">
         <v>msol0sqe6dg2v</v>
@@ -3894,10 +3894,10 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L85" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M85" t="str">
         <v>msol0sqewy04g</v>
@@ -3935,10 +3935,10 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L86" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M86" t="str">
         <v>msol0sqee580t</v>
@@ -3976,10 +3976,10 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L87" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M87" t="str">
         <v>msol0sqeiznyn</v>
@@ -4017,10 +4017,10 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L88" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M88" t="str">
         <v>msol0sqeohz5d</v>
@@ -4058,10 +4058,10 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L89" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M89" t="str">
         <v>msol0sqepq9bm</v>
@@ -4099,10 +4099,10 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L90" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M90" t="str">
         <v>msol0sqepn626</v>
@@ -4140,10 +4140,10 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L91" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M91" t="str">
         <v>msol0sqe28q4z</v>
@@ -4181,10 +4181,10 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L92" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M92" t="str">
         <v>msol0sqe56y72</v>
@@ -4222,10 +4222,10 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L93" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M93" t="str">
         <v>msol0sqeyukhl</v>
@@ -4263,10 +4263,10 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L94" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="M94" t="str">
         <v>msol2k62oicjg</v>
@@ -4304,10 +4304,10 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L95" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M95" t="str">
         <v>msribdnoza7js</v>
@@ -4345,10 +4345,10 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L96" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M96" t="str">
         <v>msribdnogrvsu</v>
@@ -4386,10 +4386,10 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L97" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M97" t="str">
         <v>msribdnote35t</v>
@@ -4427,10 +4427,10 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L98" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M98" t="str">
         <v>msribdnomnby7</v>
@@ -4468,10 +4468,10 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L99" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M99" t="str">
         <v>msribdnomwbz2</v>
@@ -4509,10 +4509,10 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L100" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M100" t="str">
         <v>msribdno4q8a4</v>
@@ -4550,10 +4550,10 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L101" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M101" t="str">
         <v>msribdno3tqby</v>
@@ -4594,10 +4594,10 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L102" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M102" t="str">
         <v>msrpyjubxmu32</v>
@@ -4645,10 +4645,10 @@
         <v/>
       </c>
       <c r="K103" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L103" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M103" t="str">
         <v>msrpyjub8lew4</v>
@@ -4695,10 +4695,10 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L104" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="M104" t="str">
         <v>msrpyjubl1s1o</v>
@@ -4736,10 +4736,10 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="L105" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="M105" t="str">
         <v>msujqqctg5pu3</v>
@@ -4777,10 +4777,10 @@
         <v/>
       </c>
       <c r="K106" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L106" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M106" t="str">
         <v>msv6eldtxyz5z</v>
@@ -4818,10 +4818,10 @@
         <v/>
       </c>
       <c r="K107" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L107" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M107" t="str">
         <v>msv6eldt79wmb</v>
@@ -4859,10 +4859,10 @@
         <v/>
       </c>
       <c r="K108" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L108" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M108" t="str">
         <v>msv6eldt2w2bn</v>
@@ -4900,10 +4900,10 @@
         <v/>
       </c>
       <c r="K109" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L109" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M109" t="str">
         <v>msv6eldt8al3c</v>
@@ -4941,10 +4941,10 @@
         <v/>
       </c>
       <c r="K110" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L110" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M110" t="str">
         <v>msv6eldt2io8e</v>
@@ -4982,10 +4982,10 @@
         <v/>
       </c>
       <c r="K111" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L111" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M111" t="str">
         <v>msv6eldt8sk8w</v>
@@ -5023,10 +5023,10 @@
         <v/>
       </c>
       <c r="K112" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L112" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M112" t="str">
         <v>msv6eldtb3gi0</v>
@@ -5064,10 +5064,10 @@
         <v/>
       </c>
       <c r="K113" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L113" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M113" t="str">
         <v>msv6eldtftuex</v>
@@ -5105,10 +5105,10 @@
         <v/>
       </c>
       <c r="K114" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="L114" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M114" t="str">
         <v>mswlrjq1miq5h</v>
@@ -5242,7 +5242,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5254,10 +5254,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L3" t="str">
-        <v>100%</v>
+        <v>6%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -5284,7 +5284,7 @@
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" customWidth="1"/>
     <col min="14" max="14" width="16.83203125" customWidth="1"/>
@@ -5360,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5372,13 +5372,13 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J2" t="str">
-        <v>60%</v>
+        <v>0%</v>
       </c>
       <c r="K2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L2" t="str">
         <v>FALSE</v>
@@ -5413,7 +5413,7 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -5425,13 +5425,13 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J3" t="str">
-        <v>40%</v>
+        <v>0%</v>
       </c>
       <c r="K3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L3" t="str">
         <v>FALSE</v>
@@ -5484,7 +5484,7 @@
         <v>50%</v>
       </c>
       <c r="K4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="L4" t="str">
         <v>FALSE</v>
@@ -5519,7 +5519,7 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -5531,13 +5531,13 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J5" t="str">
-        <v>60%</v>
+        <v>0%</v>
       </c>
       <c r="K5" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L5" t="str">
         <v>TRUE</v>
@@ -5572,7 +5572,7 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5584,13 +5584,13 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J6" t="str">
-        <v>48%</v>
+        <v>0%</v>
       </c>
       <c r="K6" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L6" t="str">
         <v>FALSE</v>
@@ -5643,7 +5643,7 @@
         <v>0%</v>
       </c>
       <c r="K7" t="str">
-        <v>Aug 11, 2026</v>
+        <v>11 Aug 2026</v>
       </c>
       <c r="L7" t="str">
         <v>FALSE</v>
@@ -5696,7 +5696,7 @@
         <v>0%</v>
       </c>
       <c r="K8" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L8" t="str">
         <v>FALSE</v>
@@ -5749,7 +5749,7 @@
         <v>25%</v>
       </c>
       <c r="K9" t="str">
-        <v>Aug 13, 2026</v>
+        <v>13 Aug 2026</v>
       </c>
       <c r="L9" t="str">
         <v>FALSE</v>
@@ -5802,7 +5802,7 @@
         <v>0%</v>
       </c>
       <c r="K10" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="L10" t="str">
         <v>FALSE</v>
@@ -5855,7 +5855,7 @@
         <v>0%</v>
       </c>
       <c r="K11" t="str">
-        <v>Aug 16, 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L11" t="str">
         <v>FALSE</v>
@@ -5896,7 +5896,7 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5952,7 +5952,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F2" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G2" t="str">
         <v>Low</v>
@@ -5964,7 +5964,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K2" t="str">
         <v>mskjvz8axp7bw</v>
@@ -5987,7 +5987,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F3" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G3" t="str">
         <v>Low</v>
@@ -5999,7 +5999,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K3" t="str">
         <v>mskjw7zqqol4f</v>
@@ -6022,7 +6022,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F4" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G4" t="str">
         <v>Medium</v>
@@ -6034,7 +6034,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K4" t="str">
         <v>mskjwecwnzinb</v>
@@ -6057,7 +6057,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F5" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G5" t="str">
         <v>Medium</v>
@@ -6069,7 +6069,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K5" t="str">
         <v>mskjwjhp0kajz</v>
@@ -6092,7 +6092,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F6" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G6" t="str">
         <v>Medium</v>
@@ -6104,7 +6104,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K6" t="str">
         <v>mskjwo8nvlf63</v>
@@ -6127,7 +6127,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F7" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G7" t="str">
         <v>Medium</v>
@@ -6139,7 +6139,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K7" t="str">
         <v>mskjwtl16gyyh</v>
@@ -6182,7 +6182,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K8" t="str">
         <v>mskk2136wm2x1</v>
@@ -6224,7 +6224,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K9" t="str">
         <v>mskk2fgb7cnrq</v>
@@ -6275,7 +6275,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Aug 8, 2026</v>
+        <v>8 Aug 2026</v>
       </c>
       <c r="K10" t="str">
         <v>mskk2w5rmle9n</v>
@@ -6298,7 +6298,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F11" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G11" t="str">
         <v>Low</v>
@@ -6310,7 +6310,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K11" t="str">
         <v>msmnd1859wbzh</v>
@@ -6333,7 +6333,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F12" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G12" t="str">
         <v>Medium</v>
@@ -6345,7 +6345,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K12" t="str">
         <v>msmnd9ppyvwo0</v>
@@ -6368,7 +6368,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F13" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G13" t="str">
         <v>Medium</v>
@@ -6380,7 +6380,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K13" t="str">
         <v>msmndgl7h0wic</v>
@@ -6403,7 +6403,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F14" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G14" t="str">
         <v>Medium</v>
@@ -6415,7 +6415,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K14" t="str">
         <v>msmndnshe7g32</v>
@@ -6438,7 +6438,7 @@
         <v>SPR-2026-W33</v>
       </c>
       <c r="F15" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G15" t="str">
         <v>Medium</v>
@@ -6450,7 +6450,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>Aug 10, 2026</v>
+        <v>10 Aug 2026</v>
       </c>
       <c r="K15" t="str">
         <v>msmndu14o94q4</v>
@@ -6485,7 +6485,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K16" t="str">
         <v>msujrugr9kf7c</v>
@@ -6520,7 +6520,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K17" t="str">
         <v>msujs3ezrjisd</v>
@@ -6555,7 +6555,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K18" t="str">
         <v>msujsdx80sust</v>
@@ -6590,7 +6590,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K19" t="str">
         <v>msujwakj566af</v>
@@ -6625,7 +6625,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K20" t="str">
         <v>msujwhc2tj26f</v>
@@ -6660,7 +6660,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K21" t="str">
         <v>msujwnnd7mozo</v>
@@ -6695,7 +6695,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K22" t="str">
         <v>msujwti0bvxmi</v>
@@ -6730,7 +6730,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K23" t="str">
         <v>msujwznrrjplj</v>
@@ -6765,7 +6765,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K24" t="str">
         <v>msujxcfxhbm9s</v>
@@ -6800,7 +6800,7 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K25" t="str">
         <v>msujximm4dgax</v>
@@ -6835,7 +6835,7 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K26" t="str">
         <v>msujy9j4854th</v>
@@ -6870,7 +6870,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K27" t="str">
         <v>msujyhn99tdy8</v>
@@ -6905,7 +6905,7 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K28" t="str">
         <v>msujynvc2jnuk</v>
@@ -6940,7 +6940,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K29" t="str">
         <v>msujyurxkz61l</v>
@@ -6975,7 +6975,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>Aug 15, 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="K30" t="str">
         <v>msujz10gszpqf</v>
@@ -7010,7 +7010,7 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K31" t="str">
         <v>mswlsudlx8ecn</v>
@@ -7045,7 +7045,7 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K32" t="str">
         <v>mswlt75tei83v</v>
@@ -7080,7 +7080,7 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K33" t="str">
         <v>mswltlzdr47og</v>
@@ -7115,7 +7115,7 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K34" t="str">
         <v>mswltz96spp72</v>
@@ -7150,7 +7150,7 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K35" t="str">
         <v>mswlubvt03mvt</v>
@@ -7185,7 +7185,7 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K36" t="str">
         <v>mswlumpdqog9b</v>
@@ -7220,7 +7220,7 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K37" t="str">
         <v>mswluuchr3p6c</v>
@@ -7255,7 +7255,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K38" t="str">
         <v>mswlv4aq2qbbw</v>
@@ -7290,7 +7290,7 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K39" t="str">
         <v>mswlvcnl0yz0v</v>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K40" t="str">
         <v>mswlvpdtxupgm</v>
@@ -7360,7 +7360,7 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K41" t="str">
         <v>mswlvv0zpgcop</v>
@@ -7395,7 +7395,7 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>Aug 17, 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="K42" t="str">
         <v>mswlw58xtbs6m</v>
@@ -7454,7 +7454,7 @@
         <v>#7c5cd8</v>
       </c>
       <c r="C3" t="str">
-        <v>msokv11v8pdah,msokz90zh9nmn,msol2au4dexr8</v>
+        <v>msokv11v8pdah,msokz90zh9nmn,msol2au4dexr8,msri9am8ug3yb</v>
       </c>
       <c r="D3" t="str">
         <v>mspj1pbk2kkn9</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -401,10 +401,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M112"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>scikit-learn/API</v>
+        <v>API</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -1914,7 +1914,7 @@
         <v>2026-08</v>
       </c>
       <c r="G37" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H37" t="str">
         <v>Medium</v>
@@ -1929,7 +1929,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>15 Aug 2026</v>
+        <v>19 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -4559,18 +4559,15 @@
         <v>msribdno3tqby</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
+    <row r="102">
       <c r="A102" t="str">
-        <v>Must Know First</v>
-      </c>
-      <c r="B102" t="str" xml:space="preserve">
-        <v xml:space="preserve">- `tf` (Core)
-- `tf.keras`
-- `tf.data`
-- `tf.estimator`</v>
+        <v>User Guide</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>Tensorflow</v>
+        <v>Scikit-Learn</v>
       </c>
       <c r="D102" t="str">
         <v>Medium</v>
@@ -4582,7 +4579,7 @@
         <v>2026-08</v>
       </c>
       <c r="G102" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="H102" t="str">
         <v>Medium</v>
@@ -4594,34 +4591,24 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>13 Aug 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="L102" t="str">
-        <v>17 Aug 2026</v>
+        <v>15 Aug 2026</v>
       </c>
       <c r="M102" t="str">
-        <v>msrpyjubxmu32</v>
-      </c>
-    </row>
-    <row r="103" xml:space="preserve">
+        <v>msujqqctg5pu3</v>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" t="str">
-        <v>Learn Next</v>
-      </c>
-      <c r="B103" t="str" xml:space="preserve">
-        <v xml:space="preserve">- `tf.math`
-- `tf.linalg`
-- `tf.io`
-- `tf.image`
-- `tf.strings`
-- `tf.random`
-- `tf.nn`
-- `tf.audio`
-- `tf.bitset`
-- `tf.debugging`
-- `tf.errors`</v>
+        <v>Get Started</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>Tensorflow</v>
+        <v>CrewAI</v>
       </c>
       <c r="D103" t="str">
         <v>Medium</v>
@@ -4633,7 +4620,7 @@
         <v>2026-08</v>
       </c>
       <c r="G103" t="str">
-        <v>To Do</v>
+        <v>In Progress</v>
       </c>
       <c r="H103" t="str">
         <v>Medium</v>
@@ -4645,33 +4632,24 @@
         <v/>
       </c>
       <c r="K103" t="str">
-        <v>13 Aug 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L103" t="str">
-        <v>13 Aug 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M103" t="str">
-        <v>msrpyjub8lew4</v>
-      </c>
-    </row>
-    <row r="104" xml:space="preserve">
+        <v>msv6eldtxyz5z</v>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" t="str">
-        <v>Explore Last</v>
-      </c>
-      <c r="B104" t="str" xml:space="preserve">
-        <v xml:space="preserve">- `tf.distribute`
-- `tf.lite`
-- `tf.saved_model`
-- `tf.sparse`
-- `tf.ragged`
-- `tf.sets`
-- `tf.signal`
-- `tf.queue`
-- `tf.compat`
-- `tf.experimental`</v>
+        <v>Guides</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>Tensorflow</v>
+        <v>CrewAI</v>
       </c>
       <c r="D104" t="str">
         <v>Medium</v>
@@ -4695,24 +4673,24 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v>13 Aug 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L104" t="str">
-        <v>13 Aug 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M104" t="str">
-        <v>msrpyjubl1s1o</v>
+        <v>msv6eldt79wmb</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>User Guide</v>
+        <v>Core Concepts</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>Scikit-Learn</v>
+        <v>CrewAI</v>
       </c>
       <c r="D105" t="str">
         <v>Medium</v>
@@ -4736,18 +4714,18 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <v>15 Aug 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="L105" t="str">
-        <v>15 Aug 2026</v>
+        <v>16 Aug 2026</v>
       </c>
       <c r="M105" t="str">
-        <v>msujqqctg5pu3</v>
+        <v>msv6eldt2w2bn</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Get Started</v>
+        <v>MCP Integration</v>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -4765,7 +4743,7 @@
         <v>2026-08</v>
       </c>
       <c r="G106" t="str">
-        <v>In Progress</v>
+        <v>To Do</v>
       </c>
       <c r="H106" t="str">
         <v>Medium</v>
@@ -4783,12 +4761,12 @@
         <v>16 Aug 2026</v>
       </c>
       <c r="M106" t="str">
-        <v>msv6eldtxyz5z</v>
+        <v>msv6eldt8al3c</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Guides</v>
+        <v>Tools</v>
       </c>
       <c r="B107" t="str">
         <v/>
@@ -4824,12 +4802,12 @@
         <v>16 Aug 2026</v>
       </c>
       <c r="M107" t="str">
-        <v>msv6eldt79wmb</v>
+        <v>msv6eldt2io8e</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Core Concepts</v>
+        <v>Observability</v>
       </c>
       <c r="B108" t="str">
         <v/>
@@ -4865,12 +4843,12 @@
         <v>16 Aug 2026</v>
       </c>
       <c r="M108" t="str">
-        <v>msv6eldt2w2bn</v>
+        <v>msv6eldt8sk8w</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>MCP Integration</v>
+        <v>Learn</v>
       </c>
       <c r="B109" t="str">
         <v/>
@@ -4906,12 +4884,12 @@
         <v>16 Aug 2026</v>
       </c>
       <c r="M109" t="str">
-        <v>msv6eldt8al3c</v>
+        <v>msv6eldtb3gi0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Tools</v>
+        <v>Telemetry</v>
       </c>
       <c r="B110" t="str">
         <v/>
@@ -4947,18 +4925,18 @@
         <v>16 Aug 2026</v>
       </c>
       <c r="M110" t="str">
-        <v>msv6eldt2io8e</v>
+        <v>msv6eldtftuex</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Observability</v>
+        <v>Guide</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>CrewAI</v>
+        <v>Tensorflow</v>
       </c>
       <c r="D111" t="str">
         <v>Medium</v>
@@ -4982,24 +4960,24 @@
         <v/>
       </c>
       <c r="K111" t="str">
-        <v>16 Aug 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="L111" t="str">
-        <v>16 Aug 2026</v>
+        <v>17 Aug 2026</v>
       </c>
       <c r="M111" t="str">
-        <v>msv6eldt8sk8w</v>
+        <v>mswlrjq1miq5h</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Learn</v>
+        <v>API</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>CrewAI</v>
+        <v>Tensorflow</v>
       </c>
       <c r="D112" t="str">
         <v>Medium</v>
@@ -5023,100 +5001,18 @@
         <v/>
       </c>
       <c r="K112" t="str">
-        <v>16 Aug 2026</v>
+        <v>19 Aug 2026</v>
       </c>
       <c r="L112" t="str">
-        <v>16 Aug 2026</v>
+        <v>19 Aug 2026</v>
       </c>
       <c r="M112" t="str">
-        <v>msv6eldtb3gi0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Telemetry</v>
-      </c>
-      <c r="B113" t="str">
-        <v/>
-      </c>
-      <c r="C113" t="str">
-        <v>CrewAI</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E113" t="str">
-        <v/>
-      </c>
-      <c r="F113" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="G113" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="H113" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="I113" t="str">
-        <v/>
-      </c>
-      <c r="J113" t="str">
-        <v/>
-      </c>
-      <c r="K113" t="str">
-        <v>16 Aug 2026</v>
-      </c>
-      <c r="L113" t="str">
-        <v>16 Aug 2026</v>
-      </c>
-      <c r="M113" t="str">
-        <v>msv6eldtftuex</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="B114" t="str">
-        <v/>
-      </c>
-      <c r="C114" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="D114" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E114" t="str">
-        <v/>
-      </c>
-      <c r="F114" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="G114" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="H114" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="I114" t="str">
-        <v/>
-      </c>
-      <c r="J114" t="str">
-        <v/>
-      </c>
-      <c r="K114" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="L114" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="M114" t="str">
-        <v>mswlrjq1miq5h</v>
+        <v>mt0a7gju3s8jt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M112"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5242,7 +5138,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5254,10 +5150,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" t="str">
-        <v>6%</v>
+        <v>0%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -5466,7 +5362,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5478,10 +5374,10 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="str">
-        <v>50%</v>
+        <v>0%</v>
       </c>
       <c r="K4" t="str">
         <v>8 Aug 2026</v>
@@ -5728,10 +5624,10 @@
         <v>Medium</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -5743,10 +5639,10 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="str">
-        <v>25%</v>
+        <v>0%</v>
       </c>
       <c r="K9" t="str">
         <v>13 Aug 2026</v>
@@ -5885,7 +5781,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K48"/>
   <cols>
     <col min="1" max="1" width="54.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
@@ -6161,16 +6057,16 @@
 - `sklearn.dummy`</v>
       </c>
       <c r="C8" t="str">
-        <v>scikit-learn/API</v>
+        <v>API</v>
       </c>
       <c r="D8" t="str">
-        <v>Scikit-Learn</v>
+        <v>Tensorflow</v>
       </c>
       <c r="E8" t="str">
         <v>SPR-2026-W33</v>
       </c>
       <c r="F8" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G8" t="str">
         <v>Medium</v>
@@ -6203,16 +6099,16 @@
 - `sklearn.exceptions`</v>
       </c>
       <c r="C9" t="str">
-        <v>scikit-learn/API</v>
+        <v>API</v>
       </c>
       <c r="D9" t="str">
-        <v>Scikit-Learn</v>
+        <v>Tensorflow</v>
       </c>
       <c r="E9" t="str">
         <v>SPR-2026-W33</v>
       </c>
       <c r="F9" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G9" t="str">
         <v>Medium</v>
@@ -6254,16 +6150,16 @@
 - `sklearn.callback`</v>
       </c>
       <c r="C10" t="str">
-        <v>scikit-learn/API</v>
+        <v>API</v>
       </c>
       <c r="D10" t="str">
-        <v>Scikit-Learn</v>
+        <v>Tensorflow</v>
       </c>
       <c r="E10" t="str">
         <v>SPR-2026-W33</v>
       </c>
       <c r="F10" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G10" t="str">
         <v>Medium</v>
@@ -6508,7 +6404,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G17" t="str">
         <v>Medium</v>
@@ -6998,7 +6894,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Done</v>
+        <v>To Do</v>
       </c>
       <c r="G31" t="str">
         <v>Medium</v>
@@ -7401,9 +7297,250 @@
         <v>mswlw58xtbs6m</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Must Know First</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v>API</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v>19 Aug 2026</v>
+      </c>
+      <c r="K43" t="str">
+        <v>mt0a8vr8s5av3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Learn Next</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v>API</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v>19 Aug 2026</v>
+      </c>
+      <c r="K44" t="str">
+        <v>mt0a95qmbqs25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Explore Last</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v>API</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v>19 Aug 2026</v>
+      </c>
+      <c r="K45" t="str">
+        <v>mt0a9dfehfnmr</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>Phase 1: Must-Know</v>
+      </c>
+      <c r="B46" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `sklearn.pipeline`
+- `sklearn.compose`
+- `sklearn.preprocessing`
+- `sklearn.impute`
+- `sklearn.model_selection`
+- `sklearn.metrics`
+- `sklearn.linear_model`
+- `sklearn.tree`
+- `sklearn.dummy`</v>
+      </c>
+      <c r="C46" t="str">
+        <v>API</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E46" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F46" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v>20 Aug 2026</v>
+      </c>
+      <c r="K46" t="str">
+        <v>mt0t571nqgpae</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>Phase 2: Next Learn (The Production Heavyweights)</v>
+      </c>
+      <c r="B47" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `sklearn.ensemble`
+- `sklearn.feature_selection`
+- `sklearn.datasets`
+- `sklearn.base`
+- `sklearn.utils`
+- `sklearn.neighbors`
+- `sklearn.naive_bayes`
+- `sklearn.exceptions`</v>
+      </c>
+      <c r="C47" t="str">
+        <v>API</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E47" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F47" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v>20 Aug 2026</v>
+      </c>
+      <c r="K47" t="str">
+        <v>mt0t5iwkj066t</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>Phase 3: Last Learn (Specialized &amp; Advanced)</v>
+      </c>
+      <c r="B48" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `sklearn.cluster`
+- `sklearn.decomposition`
+- `sklearn.inspect`
+- `sklearn.feature_extraction`
+- `sklearn.calibration`
+- `sklearn.svm`
+- `sklearn.manifold`
+- `sklearn.mixture`
+- `sklearn.covariance`
+- `sklearn.cross_decomposition`
+- `sklearn.semi_supervised`
+- `sklearn.neural_network`
+- `sklearn.discriminant_analysis`
+- `sklearn.isotonic`
+- `sklearn.kernel_approximation`
+- `sklearn.random_projection`
+- `sklearn.callback`</v>
+      </c>
+      <c r="C48" t="str">
+        <v>API</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E48" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F48" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v>20 Aug 2026</v>
+      </c>
+      <c r="K48" t="str">
+        <v>mt0t5y3omv18v</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7454,7 +7591,7 @@
         <v>#7c5cd8</v>
       </c>
       <c r="C3" t="str">
-        <v>msokv11v8pdah,msokz90zh9nmn,msol2au4dexr8,msri9am8ug3yb</v>
+        <v>msokv11v8pdah,msokz90zh9nmn,msol2au4dexr8,msuk6qp8zwkp3</v>
       </c>
       <c r="D3" t="str">
         <v>mspj1pbk2kkn9</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -1914,7 +1914,7 @@
         <v>2026-08</v>
       </c>
       <c r="G37" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H37" t="str">
         <v>Medium</v>
@@ -1929,7 +1929,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L37" t="str">
-        <v>19 Aug 2026</v>
+        <v>20 Aug 2026</v>
       </c>
       <c r="M37" t="str">
         <v>mskk12tpxnz6q</v>
@@ -4989,7 +4989,7 @@
         <v>2026-08</v>
       </c>
       <c r="G112" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H112" t="str">
         <v>Medium</v>
@@ -5004,7 +5004,7 @@
         <v>19 Aug 2026</v>
       </c>
       <c r="L112" t="str">
-        <v>19 Aug 2026</v>
+        <v>20 Aug 2026</v>
       </c>
       <c r="M112" t="str">
         <v>mt0a7gju3s8jt</v>
@@ -5138,7 +5138,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5150,10 +5150,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L3" t="str">
-        <v>0%</v>
+        <v>6%</v>
       </c>
       <c r="M3" t="str">
         <v>mskjojd2g5ua7</v>
@@ -5362,7 +5362,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5374,10 +5374,10 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="str">
-        <v>0%</v>
+        <v>50%</v>
       </c>
       <c r="K4" t="str">
         <v>8 Aug 2026</v>
@@ -5627,7 +5627,7 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -5639,10 +5639,10 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="str">
-        <v>0%</v>
+        <v>50%</v>
       </c>
       <c r="K9" t="str">
         <v>13 Aug 2026</v>
@@ -5781,9 +5781,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K45"/>
   <cols>
-    <col min="1" max="1" width="54.83203125" customWidth="1"/>
+    <col min="1" max="1" width="51.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
     <col min="3" max="3" width="19.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
@@ -6041,11 +6041,1258 @@
         <v>mskjwtl16gyyh</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
+    <row r="8">
       <c r="A8" t="str">
-        <v>🟥 Phase 1: Must-Know (The Core Foundation)</v>
-      </c>
-      <c r="B8" t="str" xml:space="preserve">
+        <v>Feature Interaction Constraints</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D8" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E8" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F8" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K8" t="str">
+        <v>msmnd1859wbzh</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Survival Analysis with Accelerated Failure Time</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D9" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E9" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F9" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K9" t="str">
+        <v>msmnd9ppyvwo0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Categorical Data</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D10" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E10" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F10" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K10" t="str">
+        <v>msmndgl7h0wic</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Multiple Outputs</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D11" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E11" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F11" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K11" t="str">
+        <v>msmndnshe7g32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Random Forests(TM) in XGBoost</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>XGBoost Tutorials</v>
+      </c>
+      <c r="D12" t="str">
+        <v>XGBoost</v>
+      </c>
+      <c r="E12" t="str">
+        <v>SPR-2026-W33</v>
+      </c>
+      <c r="F12" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>10 Aug 2026</v>
+      </c>
+      <c r="K12" t="str">
+        <v>msmndu14o94q4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1. Supervised learning</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K13" t="str">
+        <v>msujrugr9kf7c</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2. Unsupervised learning</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K14" t="str">
+        <v>msujs3ezrjisd</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3. Model selection and evaluation</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K15" t="str">
+        <v>msujsdx80sust</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>4. Metadata Routing</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K16" t="str">
+        <v>msujwakj566af</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5. Inspection</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K17" t="str">
+        <v>msujwhc2tj26f</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>6. Visualizations</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K18" t="str">
+        <v>msujwnnd7mozo</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>7. Callbacks</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K19" t="str">
+        <v>msujwti0bvxmi</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>8. Dataset transformations</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K20" t="str">
+        <v>msujwznrrjplj</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>9. Dataset loading utilities</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K21" t="str">
+        <v>msujxcfxhbm9s</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>10. Computing with scikit-learn</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K22" t="str">
+        <v>msujximm4dgax</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>11. Model persistence</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K23" t="str">
+        <v>msujy9j4854th</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>12. Common pitfalls and recommended practices</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K24" t="str">
+        <v>msujyhn99tdy8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>13. Data Interoperability</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K25" t="str">
+        <v>msujynvc2jnuk</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>14. Choosing the right estimator</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K26" t="str">
+        <v>msujyurxkz61l</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>15. External Resources, Videos and Talks</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v>15 Aug 2026</v>
+      </c>
+      <c r="K27" t="str">
+        <v>msujz10gszpqf</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Tensorflow basics</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K28" t="str">
+        <v>mswlsudlx8ecn</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Keras</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K29" t="str">
+        <v>mswlt75tei83v</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Build with Core</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K30" t="str">
+        <v>mswltlzdr47og</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Tensorflow in depth</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K31" t="str">
+        <v>mswltz96spp72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Customization</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K32" t="str">
+        <v>mswlubvt03mvt</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Data input pipelines</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K33" t="str">
+        <v>mswlumpdqog9b</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Import and export</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K34" t="str">
+        <v>mswluuchr3p6c</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Accelerators</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K35" t="str">
+        <v>mswlv4aq2qbbw</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K36" t="str">
+        <v>mswlvcnl0yz0v</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Model Garden</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K37" t="str">
+        <v>mswlvpdtxupgm</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Estimators</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K38" t="str">
+        <v>mswlvv0zpgcop</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Appendix</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v>Guide</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v>17 Aug 2026</v>
+      </c>
+      <c r="K39" t="str">
+        <v>mswlw58xtbs6m</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>Must Know First</v>
+      </c>
+      <c r="B40" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `tf` (Core)
+- `tf.keras`
+- `tf.data`
+- `tf.estimator`</v>
+      </c>
+      <c r="C40" t="str">
+        <v>API</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>Done</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v>19 Aug 2026</v>
+      </c>
+      <c r="K40" t="str">
+        <v>mt0a8vr8s5av3</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>Learn Next</v>
+      </c>
+      <c r="B41" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `tf.math`
+- `tf.linalg`
+- `tf.io`
+- `tf.image`
+- `tf.strings`
+- `tf.random`
+- `tf.nn`
+- `tf.audio`
+- `tf.bitset`
+- `tf.debugging`
+- `tf.errors`</v>
+      </c>
+      <c r="C41" t="str">
+        <v>API</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>Done</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v>19 Aug 2026</v>
+      </c>
+      <c r="K41" t="str">
+        <v>mt0a95qmbqs25</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>Explore Last</v>
+      </c>
+      <c r="B42" t="str" xml:space="preserve">
+        <v xml:space="preserve">- `tf.distribute`
+- `tf.lite`
+- `tf.saved_model`
+- `tf.sparse`
+- `tf.ragged`
+- `tf.sets`
+- `tf.signal`
+- `tf.queue`
+- `tf.compat`
+- `tf.experimental`</v>
+      </c>
+      <c r="C42" t="str">
+        <v>API</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Tensorflow</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>Done</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v>19 Aug 2026</v>
+      </c>
+      <c r="K42" t="str">
+        <v>mt0a9dfehfnmr</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>Phase 1: Must-Know</v>
+      </c>
+      <c r="B43" t="str" xml:space="preserve">
         <v xml:space="preserve">- `sklearn.pipeline`
 - `sklearn.compose`
 - `sklearn.preprocessing`
@@ -6056,39 +7303,39 @@
 - `sklearn.tree`
 - `sklearn.dummy`</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C43" t="str">
         <v>API</v>
       </c>
-      <c r="D8" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E8" t="str">
+      <c r="D43" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E43" t="str">
         <v>SPR-2026-W33</v>
       </c>
-      <c r="F8" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v>8 Aug 2026</v>
-      </c>
-      <c r="K8" t="str">
-        <v>mskk2136wm2x1</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str">
-        <v>🟨 Phase 2: Next Learn (The Production Heavyweights)</v>
-      </c>
-      <c r="B9" t="str" xml:space="preserve">
+      <c r="F43" t="str">
+        <v>Done</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v>20 Aug 2026</v>
+      </c>
+      <c r="K43" t="str">
+        <v>mt0t571nqgpae</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>Phase 2: Next Learn (The Production Heavyweights)</v>
+      </c>
+      <c r="B44" t="str" xml:space="preserve">
         <v xml:space="preserve">- `sklearn.ensemble`
 - `sklearn.feature_selection`
 - `sklearn.datasets`
@@ -6098,39 +7345,39 @@
 - `sklearn.naive_bayes`
 - `sklearn.exceptions`</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C44" t="str">
         <v>API</v>
       </c>
-      <c r="D9" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E9" t="str">
+      <c r="D44" t="str">
+        <v>Scikit-Learn</v>
+      </c>
+      <c r="E44" t="str">
         <v>SPR-2026-W33</v>
       </c>
-      <c r="F9" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v>8 Aug 2026</v>
-      </c>
-      <c r="K9" t="str">
-        <v>mskk2fgb7cnrq</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
-        <v>🟩 Phase 3: Last Learn (Specialized &amp; Advanced)</v>
-      </c>
-      <c r="B10" t="str" xml:space="preserve">
+      <c r="F44" t="str">
+        <v>Done</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v>20 Aug 2026</v>
+      </c>
+      <c r="K44" t="str">
+        <v>mt0t5iwkj066t</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>Phase 3: Last Learn (Specialized &amp; Advanced)</v>
+      </c>
+      <c r="B45" t="str" xml:space="preserve">
         <v xml:space="preserve">- `sklearn.cluster`
 - `sklearn.decomposition`
 - `sklearn.inspect`
@@ -6149,1242 +7396,17 @@
 - `sklearn.random_projection`
 - `sklearn.callback`</v>
       </c>
-      <c r="C10" t="str">
-        <v>API</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E10" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F10" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v>8 Aug 2026</v>
-      </c>
-      <c r="K10" t="str">
-        <v>mskk2w5rmle9n</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Feature Interaction Constraints</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v>XGBoost Tutorials</v>
-      </c>
-      <c r="D11" t="str">
-        <v>XGBoost</v>
-      </c>
-      <c r="E11" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F11" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v>10 Aug 2026</v>
-      </c>
-      <c r="K11" t="str">
-        <v>msmnd1859wbzh</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Survival Analysis with Accelerated Failure Time</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v>XGBoost Tutorials</v>
-      </c>
-      <c r="D12" t="str">
-        <v>XGBoost</v>
-      </c>
-      <c r="E12" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F12" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v>10 Aug 2026</v>
-      </c>
-      <c r="K12" t="str">
-        <v>msmnd9ppyvwo0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Categorical Data</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v>XGBoost Tutorials</v>
-      </c>
-      <c r="D13" t="str">
-        <v>XGBoost</v>
-      </c>
-      <c r="E13" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F13" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v>10 Aug 2026</v>
-      </c>
-      <c r="K13" t="str">
-        <v>msmndgl7h0wic</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Multiple Outputs</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v>XGBoost Tutorials</v>
-      </c>
-      <c r="D14" t="str">
-        <v>XGBoost</v>
-      </c>
-      <c r="E14" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F14" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v>10 Aug 2026</v>
-      </c>
-      <c r="K14" t="str">
-        <v>msmndnshe7g32</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Random Forests(TM) in XGBoost</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>XGBoost Tutorials</v>
-      </c>
-      <c r="D15" t="str">
-        <v>XGBoost</v>
-      </c>
-      <c r="E15" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F15" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v>10 Aug 2026</v>
-      </c>
-      <c r="K15" t="str">
-        <v>msmndu14o94q4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>1. Supervised learning</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K16" t="str">
-        <v>msujrugr9kf7c</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2. Unsupervised learning</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K17" t="str">
-        <v>msujs3ezrjisd</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3. Model selection and evaluation</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K18" t="str">
-        <v>msujsdx80sust</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>4. Metadata Routing</v>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K19" t="str">
-        <v>msujwakj566af</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>5. Inspection</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K20" t="str">
-        <v>msujwhc2tj26f</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>6. Visualizations</v>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K21" t="str">
-        <v>msujwnnd7mozo</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>7. Callbacks</v>
-      </c>
-      <c r="B22" t="str">
-        <v/>
-      </c>
-      <c r="C22" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K22" t="str">
-        <v>msujwti0bvxmi</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>8. Dataset transformations</v>
-      </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K23" t="str">
-        <v>msujwznrrjplj</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>9. Dataset loading utilities</v>
-      </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K24" t="str">
-        <v>msujxcfxhbm9s</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>10. Computing with scikit-learn</v>
-      </c>
-      <c r="B25" t="str">
-        <v/>
-      </c>
-      <c r="C25" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K25" t="str">
-        <v>msujximm4dgax</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>11. Model persistence</v>
-      </c>
-      <c r="B26" t="str">
-        <v/>
-      </c>
-      <c r="C26" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K26" t="str">
-        <v>msujy9j4854th</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>12. Common pitfalls and recommended practices</v>
-      </c>
-      <c r="B27" t="str">
-        <v/>
-      </c>
-      <c r="C27" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K27" t="str">
-        <v>msujyhn99tdy8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>13. Data Interoperability</v>
-      </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K28" t="str">
-        <v>msujynvc2jnuk</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>14. Choosing the right estimator</v>
-      </c>
-      <c r="B29" t="str">
-        <v/>
-      </c>
-      <c r="C29" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K29" t="str">
-        <v>msujyurxkz61l</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>15. External Resources, Videos and Talks</v>
-      </c>
-      <c r="B30" t="str">
-        <v/>
-      </c>
-      <c r="C30" t="str">
-        <v>User Guide</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-      <c r="F30" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <v>15 Aug 2026</v>
-      </c>
-      <c r="K30" t="str">
-        <v>msujz10gszpqf</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Tensorflow basics</v>
-      </c>
-      <c r="B31" t="str">
-        <v/>
-      </c>
-      <c r="C31" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-      <c r="J31" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K31" t="str">
-        <v>mswlsudlx8ecn</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Keras</v>
-      </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="J32" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K32" t="str">
-        <v>mswlt75tei83v</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Build with Core</v>
-      </c>
-      <c r="B33" t="str">
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G33" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <v/>
-      </c>
-      <c r="J33" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K33" t="str">
-        <v>mswltlzdr47og</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Tensorflow in depth</v>
-      </c>
-      <c r="B34" t="str">
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-      <c r="F34" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
-      <c r="J34" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K34" t="str">
-        <v>mswltz96spp72</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Customization</v>
-      </c>
-      <c r="B35" t="str">
-        <v/>
-      </c>
-      <c r="C35" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
-      <c r="J35" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K35" t="str">
-        <v>mswlubvt03mvt</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Data input pipelines</v>
-      </c>
-      <c r="B36" t="str">
-        <v/>
-      </c>
-      <c r="C36" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
-      <c r="F36" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <v/>
-      </c>
-      <c r="J36" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K36" t="str">
-        <v>mswlumpdqog9b</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Import and export</v>
-      </c>
-      <c r="B37" t="str">
-        <v/>
-      </c>
-      <c r="C37" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
-      <c r="I37" t="str">
-        <v/>
-      </c>
-      <c r="J37" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K37" t="str">
-        <v>mswluuchr3p6c</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Accelerators</v>
-      </c>
-      <c r="B38" t="str">
-        <v/>
-      </c>
-      <c r="C38" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-      <c r="F38" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38" t="str">
-        <v/>
-      </c>
-      <c r="J38" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K38" t="str">
-        <v>mswlv4aq2qbbw</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Performance</v>
-      </c>
-      <c r="B39" t="str">
-        <v/>
-      </c>
-      <c r="C39" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-      <c r="J39" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K39" t="str">
-        <v>mswlvcnl0yz0v</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Model Garden</v>
-      </c>
-      <c r="B40" t="str">
-        <v/>
-      </c>
-      <c r="C40" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G40" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40" t="str">
-        <v/>
-      </c>
-      <c r="J40" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K40" t="str">
-        <v>mswlvpdtxupgm</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Estimators</v>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G41" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
-      <c r="J41" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K41" t="str">
-        <v>mswlvv0zpgcop</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Appendix</v>
-      </c>
-      <c r="B42" t="str">
-        <v/>
-      </c>
-      <c r="C42" t="str">
-        <v>Guide</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-      <c r="J42" t="str">
-        <v>17 Aug 2026</v>
-      </c>
-      <c r="K42" t="str">
-        <v>mswlw58xtbs6m</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Must Know First</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
-      </c>
-      <c r="C43" t="str">
-        <v>API</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G43" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="J43" t="str">
-        <v>19 Aug 2026</v>
-      </c>
-      <c r="K43" t="str">
-        <v>mt0a8vr8s5av3</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Learn Next</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
-      </c>
-      <c r="C44" t="str">
-        <v>API</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Tensorflow</v>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v/>
-      </c>
-      <c r="J44" t="str">
-        <v>19 Aug 2026</v>
-      </c>
-      <c r="K44" t="str">
-        <v>mt0a95qmbqs25</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Explore Last</v>
-      </c>
-      <c r="B45" t="str">
-        <v/>
-      </c>
       <c r="C45" t="str">
         <v>API</v>
       </c>
       <c r="D45" t="str">
-        <v>Tensorflow</v>
+        <v>Scikit-Learn</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>SPR-2026-W33</v>
       </c>
       <c r="F45" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="G45" t="str">
         <v>Medium</v>
@@ -7396,151 +7418,15 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>19 Aug 2026</v>
+        <v>20 Aug 2026</v>
       </c>
       <c r="K45" t="str">
-        <v>mt0a9dfehfnmr</v>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46" t="str">
-        <v>Phase 1: Must-Know</v>
-      </c>
-      <c r="B46" t="str" xml:space="preserve">
-        <v xml:space="preserve">- `sklearn.pipeline`
-- `sklearn.compose`
-- `sklearn.preprocessing`
-- `sklearn.impute`
-- `sklearn.model_selection`
-- `sklearn.metrics`
-- `sklearn.linear_model`
-- `sklearn.tree`
-- `sklearn.dummy`</v>
-      </c>
-      <c r="C46" t="str">
-        <v>API</v>
-      </c>
-      <c r="D46" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E46" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F46" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G46" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-      <c r="I46" t="str">
-        <v/>
-      </c>
-      <c r="J46" t="str">
-        <v>20 Aug 2026</v>
-      </c>
-      <c r="K46" t="str">
-        <v>mt0t571nqgpae</v>
-      </c>
-    </row>
-    <row r="47" xml:space="preserve">
-      <c r="A47" t="str">
-        <v>Phase 2: Next Learn (The Production Heavyweights)</v>
-      </c>
-      <c r="B47" t="str" xml:space="preserve">
-        <v xml:space="preserve">- `sklearn.ensemble`
-- `sklearn.feature_selection`
-- `sklearn.datasets`
-- `sklearn.base`
-- `sklearn.utils`
-- `sklearn.neighbors`
-- `sklearn.naive_bayes`
-- `sklearn.exceptions`</v>
-      </c>
-      <c r="C47" t="str">
-        <v>API</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E47" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F47" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G47" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H47" t="str">
-        <v/>
-      </c>
-      <c r="I47" t="str">
-        <v/>
-      </c>
-      <c r="J47" t="str">
-        <v>20 Aug 2026</v>
-      </c>
-      <c r="K47" t="str">
-        <v>mt0t5iwkj066t</v>
-      </c>
-    </row>
-    <row r="48" xml:space="preserve">
-      <c r="A48" t="str">
-        <v>Phase 3: Last Learn (Specialized &amp; Advanced)</v>
-      </c>
-      <c r="B48" t="str" xml:space="preserve">
-        <v xml:space="preserve">- `sklearn.cluster`
-- `sklearn.decomposition`
-- `sklearn.inspect`
-- `sklearn.feature_extraction`
-- `sklearn.calibration`
-- `sklearn.svm`
-- `sklearn.manifold`
-- `sklearn.mixture`
-- `sklearn.covariance`
-- `sklearn.cross_decomposition`
-- `sklearn.semi_supervised`
-- `sklearn.neural_network`
-- `sklearn.discriminant_analysis`
-- `sklearn.isotonic`
-- `sklearn.kernel_approximation`
-- `sklearn.random_projection`
-- `sklearn.callback`</v>
-      </c>
-      <c r="C48" t="str">
-        <v>API</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Scikit-Learn</v>
-      </c>
-      <c r="E48" t="str">
-        <v>SPR-2026-W33</v>
-      </c>
-      <c r="F48" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="G48" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H48" t="str">
-        <v/>
-      </c>
-      <c r="I48" t="str">
-        <v/>
-      </c>
-      <c r="J48" t="str">
-        <v>20 Aug 2026</v>
-      </c>
-      <c r="K48" t="str">
         <v>mt0t5y3omv18v</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K45"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -1094,7 +1094,7 @@
         <v>2026-08</v>
       </c>
       <c r="G17" t="str">
-        <v>To Do</v>
+        <v>In Progress</v>
       </c>
       <c r="H17" t="str">
         <v>Low</v>
@@ -1109,7 +1109,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L17" t="str">
-        <v>10 Aug 2026</v>
+        <v>20 Aug 2026</v>
       </c>
       <c r="M17" t="str">
         <v>mskjuazrvir8z</v>
@@ -1135,7 +1135,7 @@
         <v>2026-08</v>
       </c>
       <c r="G18" t="str">
-        <v>To Do</v>
+        <v>In Progress</v>
       </c>
       <c r="H18" t="str">
         <v>Low</v>
@@ -1150,7 +1150,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L18" t="str">
-        <v>10 Aug 2026</v>
+        <v>20 Aug 2026</v>
       </c>
       <c r="M18" t="str">
         <v>mskjuazrg15tu</v>
@@ -1176,7 +1176,7 @@
         <v>2026-08</v>
       </c>
       <c r="G19" t="str">
-        <v>To Do</v>
+        <v>In Progress</v>
       </c>
       <c r="H19" t="str">
         <v>Low</v>
@@ -1191,7 +1191,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L19" t="str">
-        <v>10 Aug 2026</v>
+        <v>20 Aug 2026</v>
       </c>
       <c r="M19" t="str">
         <v>mskjuazrw6ksx</v>
@@ -1217,7 +1217,7 @@
         <v>2026-08</v>
       </c>
       <c r="G20" t="str">
-        <v>To Do</v>
+        <v>In Progress</v>
       </c>
       <c r="H20" t="str">
         <v>Low</v>
@@ -1232,7 +1232,7 @@
         <v>8 Aug 2026</v>
       </c>
       <c r="L20" t="str">
-        <v>10 Aug 2026</v>
+        <v>20 Aug 2026</v>
       </c>
       <c r="M20" t="str">
         <v>mskjuazrdkxmj</v>
@@ -2980,7 +2980,7 @@
         <v>2026-08</v>
       </c>
       <c r="G63" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H63" t="str">
         <v>Medium</v>
@@ -2995,7 +2995,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L63" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M63" t="str">
         <v>msol0sqedwrwb</v>
@@ -3021,7 +3021,7 @@
         <v>2026-08</v>
       </c>
       <c r="G64" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H64" t="str">
         <v>Medium</v>
@@ -3036,7 +3036,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L64" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M64" t="str">
         <v>msol0sqengvk7</v>
@@ -3062,7 +3062,7 @@
         <v>2026-08</v>
       </c>
       <c r="G65" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H65" t="str">
         <v>Medium</v>
@@ -3077,7 +3077,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L65" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M65" t="str">
         <v>msol0sqeuws7d</v>
@@ -3103,7 +3103,7 @@
         <v>2026-08</v>
       </c>
       <c r="G66" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H66" t="str">
         <v>Medium</v>
@@ -3118,7 +3118,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L66" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M66" t="str">
         <v>msol0sqekcfzc</v>
@@ -3144,7 +3144,7 @@
         <v>2026-08</v>
       </c>
       <c r="G67" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H67" t="str">
         <v>Medium</v>
@@ -3159,7 +3159,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L67" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M67" t="str">
         <v>msol0sqemrzds</v>
@@ -3185,7 +3185,7 @@
         <v>2026-08</v>
       </c>
       <c r="G68" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H68" t="str">
         <v>Medium</v>
@@ -3200,7 +3200,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L68" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M68" t="str">
         <v>msol0sqepq0ch</v>
@@ -3226,7 +3226,7 @@
         <v>2026-08</v>
       </c>
       <c r="G69" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H69" t="str">
         <v>Medium</v>
@@ -3241,7 +3241,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L69" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M69" t="str">
         <v>msol0sqe12vt4</v>
@@ -3267,7 +3267,7 @@
         <v>2026-08</v>
       </c>
       <c r="G70" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H70" t="str">
         <v>Medium</v>
@@ -3282,7 +3282,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L70" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M70" t="str">
         <v>msol0sqelotvw</v>
@@ -3308,7 +3308,7 @@
         <v>2026-08</v>
       </c>
       <c r="G71" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H71" t="str">
         <v>Medium</v>
@@ -3323,7 +3323,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L71" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M71" t="str">
         <v>msol0sqe3ckax</v>
@@ -3349,7 +3349,7 @@
         <v>2026-08</v>
       </c>
       <c r="G72" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H72" t="str">
         <v>Medium</v>
@@ -3364,7 +3364,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L72" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M72" t="str">
         <v>msol0sqe7neja</v>
@@ -3390,7 +3390,7 @@
         <v>2026-08</v>
       </c>
       <c r="G73" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H73" t="str">
         <v>Medium</v>
@@ -3405,7 +3405,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L73" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M73" t="str">
         <v>msol0sqemccjp</v>
@@ -3431,7 +3431,7 @@
         <v>2026-08</v>
       </c>
       <c r="G74" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H74" t="str">
         <v>Medium</v>
@@ -3446,7 +3446,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L74" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M74" t="str">
         <v>msol0sqei4fpl</v>
@@ -3472,7 +3472,7 @@
         <v>2026-08</v>
       </c>
       <c r="G75" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H75" t="str">
         <v>Medium</v>
@@ -3487,7 +3487,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L75" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M75" t="str">
         <v>msol0sqe37ejp</v>
@@ -3513,7 +3513,7 @@
         <v>2026-08</v>
       </c>
       <c r="G76" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H76" t="str">
         <v>Medium</v>
@@ -3528,7 +3528,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L76" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M76" t="str">
         <v>msol0sqe2tdno</v>
@@ -3554,7 +3554,7 @@
         <v>2026-08</v>
       </c>
       <c r="G77" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H77" t="str">
         <v>Medium</v>
@@ -3569,7 +3569,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L77" t="str">
-        <v>12 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M77" t="str">
         <v>msol0sqe3wknl</v>
@@ -3595,7 +3595,7 @@
         <v>2026-08</v>
       </c>
       <c r="G78" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H78" t="str">
         <v>Medium</v>
@@ -3610,7 +3610,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L78" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M78" t="str">
         <v>msol0sqejzchq</v>
@@ -3636,7 +3636,7 @@
         <v>2026-08</v>
       </c>
       <c r="G79" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H79" t="str">
         <v>Medium</v>
@@ -3651,7 +3651,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L79" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M79" t="str">
         <v>msol0sqet2uhb</v>
@@ -3677,7 +3677,7 @@
         <v>2026-08</v>
       </c>
       <c r="G80" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H80" t="str">
         <v>Medium</v>
@@ -3692,7 +3692,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L80" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M80" t="str">
         <v>msol0sqe5wsbz</v>
@@ -3718,7 +3718,7 @@
         <v>2026-08</v>
       </c>
       <c r="G81" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H81" t="str">
         <v>Medium</v>
@@ -3733,7 +3733,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L81" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M81" t="str">
         <v>msol0sqezkuii</v>
@@ -3759,7 +3759,7 @@
         <v>2026-08</v>
       </c>
       <c r="G82" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H82" t="str">
         <v>Medium</v>
@@ -3774,7 +3774,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L82" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M82" t="str">
         <v>msol0sqe4p67x</v>
@@ -3800,7 +3800,7 @@
         <v>2026-08</v>
       </c>
       <c r="G83" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H83" t="str">
         <v>Medium</v>
@@ -3815,7 +3815,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L83" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M83" t="str">
         <v>msol0sqehxbfj</v>
@@ -3841,7 +3841,7 @@
         <v>2026-08</v>
       </c>
       <c r="G84" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H84" t="str">
         <v>Medium</v>
@@ -3856,7 +3856,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L84" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M84" t="str">
         <v>msol0sqe6dg2v</v>
@@ -3882,7 +3882,7 @@
         <v>2026-08</v>
       </c>
       <c r="G85" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H85" t="str">
         <v>Medium</v>
@@ -3897,7 +3897,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L85" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M85" t="str">
         <v>msol0sqewy04g</v>
@@ -3923,7 +3923,7 @@
         <v>2026-08</v>
       </c>
       <c r="G86" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H86" t="str">
         <v>Medium</v>
@@ -3938,7 +3938,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L86" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M86" t="str">
         <v>msol0sqee580t</v>
@@ -3964,7 +3964,7 @@
         <v>2026-08</v>
       </c>
       <c r="G87" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H87" t="str">
         <v>Medium</v>
@@ -3979,7 +3979,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L87" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M87" t="str">
         <v>msol0sqeiznyn</v>
@@ -4005,7 +4005,7 @@
         <v>2026-08</v>
       </c>
       <c r="G88" t="str">
-        <v>To Do</v>
+        <v>Done</v>
       </c>
       <c r="H88" t="str">
         <v>Medium</v>
@@ -4020,7 +4020,7 @@
         <v>11 Aug 2026</v>
       </c>
       <c r="L88" t="str">
-        <v>11 Aug 2026</v>
+        <v>21 Aug 2026</v>
       </c>
       <c r="M88" t="str">
         <v>msol0sqeohz5d</v>
@@ -5141,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5150,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L3" t="str">
         <v>6%</v>
@@ -5312,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J3" t="str">
         <v>0%</v>
@@ -5468,7 +5468,7 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J6" t="str">
-        <v>0%</v>
+        <v>84%</v>
       </c>
       <c r="K6" t="str">
         <v>11 Aug 2026</v>
@@ -7307,7 +7307,7 @@
         <v>API</v>
       </c>
       <c r="D43" t="str">
-        <v>Scikit-Learn</v>
+        <v>Tensorflow</v>
       </c>
       <c r="E43" t="str">
         <v>SPR-2026-W33</v>
@@ -7349,7 +7349,7 @@
         <v>API</v>
       </c>
       <c r="D44" t="str">
-        <v>Scikit-Learn</v>
+        <v>Tensorflow</v>
       </c>
       <c r="E44" t="str">
         <v>SPR-2026-W33</v>
@@ -7400,7 +7400,7 @@
         <v>API</v>
       </c>
       <c r="D45" t="str">
-        <v>Scikit-Learn</v>
+        <v>Tensorflow</v>
       </c>
       <c r="E45" t="str">
         <v>SPR-2026-W33</v>

--- a/db/tracker.xlsx
+++ b/db/tracker.xlsx
@@ -453,19 +453,19 @@
   <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.83203125" customWidth="1" min="1" max="1"/>
-    <col width="13.83203125" customWidth="1" min="2" max="2"/>
-    <col width="16.83203125" customWidth="1" min="3" max="3"/>
-    <col width="15.83203125" customWidth="1" min="4" max="4"/>
-    <col width="14.83203125" customWidth="1" min="5" max="5"/>
-    <col width="10.83203125" customWidth="1" min="6" max="6"/>
-    <col width="13.83203125" customWidth="1" min="7" max="7"/>
-    <col width="10.83203125" customWidth="1" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" min="10" max="10"/>
-    <col width="13.83203125" customWidth="1" min="11" max="11"/>
-    <col width="13.83203125" customWidth="1" min="12" max="12"/>
-    <col width="15.83203125" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>15 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5856,19 +5856,19 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.83203125" customWidth="1" min="1" max="1"/>
-    <col width="10.83203125" customWidth="1" min="2" max="2"/>
-    <col width="12.83203125" customWidth="1" min="3" max="3"/>
-    <col width="12.83203125" customWidth="1" min="4" max="4"/>
-    <col width="10.83203125" customWidth="1" min="5" max="5"/>
-    <col width="13.83203125" customWidth="1" min="6" max="6"/>
-    <col width="10.83203125" customWidth="1" min="7" max="7"/>
-    <col width="13.83203125" customWidth="1" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" min="10" max="10"/>
-    <col width="10.83203125" customWidth="1" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" min="12" max="12"/>
-    <col width="15.83203125" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6009,27 +6009,27 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>18</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>13</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -6052,23 +6052,23 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22.83203125" customWidth="1" min="1" max="1"/>
-    <col width="13.83203125" customWidth="1" min="2" max="2"/>
-    <col width="10.83203125" customWidth="1" min="3" max="3"/>
-    <col width="13.83203125" customWidth="1" min="4" max="4"/>
-    <col width="10.83203125" customWidth="1" min="5" max="5"/>
-    <col width="13.83203125" customWidth="1" min="6" max="6"/>
-    <col width="10.83203125" customWidth="1" min="7" max="7"/>
-    <col width="10.83203125" customWidth="1" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" min="10" max="10"/>
-    <col width="13.83203125" customWidth="1" min="11" max="11"/>
-    <col width="18.83203125" customWidth="1" min="12" max="12"/>
-    <col width="16.83203125" customWidth="1" min="13" max="13"/>
-    <col width="16.83203125" customWidth="1" min="14" max="14"/>
-    <col width="14.83203125" customWidth="1" min="15" max="15"/>
-    <col width="20.83203125" customWidth="1" min="16" max="16"/>
-    <col width="15.83203125" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6169,22 +6169,22 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>15</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>15</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -6200,6 +6200,14 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>mskjmm1ia28u3,mskjmm1i9x9ut,mskjmm1i0an4d,mskjmm1ir8uys,mskjmm1in1491</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -6219,22 +6227,22 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>20</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>16</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -6254,17 +6262,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Daily Focus</t>
+          <t>Afternoon Focus</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -6289,27 +6297,27 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
+      <c r="I4">
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6319,7 +6327,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Morning Focus</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -6329,12 +6342,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>mskk12tpxnz6q</t>
+          <t>mskk12tpxnz6q,msujqqctg5pu3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -6354,23 +6367,23 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>25</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>25</v>
+      <c r="I5">
+        <v>20</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -6394,12 +6407,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>msokv11v8pdah</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Evening Focus</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>msokvqo38bfww,msokvqo3tpfld,msokvqo323mt3,msokvqo3fjm2f,msokvqo34hlxf</t>
         </is>
       </c>
     </row>
@@ -6414,27 +6437,27 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>31</v>
       </c>
-      <c r="E6" t="n">
-        <v>26</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="F6">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>5</v>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>31</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -6447,21 +6470,14 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
+      <c r="N6"/>
+      <c r="O6"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>msokz90zh9nmn</t>
         </is>
       </c>
+      <c r="M6"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6474,22 +6490,22 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -6512,6 +6528,9 @@
           <t>msol2au4dexr8</t>
         </is>
       </c>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6524,23 +6543,23 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7</v>
+      <c r="I8">
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -6554,12 +6573,32 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>msri9am8ug3yb</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Night Focus (Before 9 PM)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>msribdnoza7js,msribdnogrvsu,msribdnote35t</t>
         </is>
       </c>
     </row>
@@ -6574,27 +6613,27 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
+      <c r="F9">
         <v>0</v>
       </c>
-      <c r="H9" t="n">
+      <c r="G9">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -6607,21 +6646,14 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
+      <c r="N9"/>
+      <c r="O9"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>msrprx3yrm2my</t>
         </is>
       </c>
+      <c r="M9"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6667,21 +6699,14 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
+      <c r="N10"/>
+      <c r="O10"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>msuk6qp8zwkp3</t>
         </is>
       </c>
+      <c r="M10"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6694,23 +6719,23 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
+      <c r="G11">
         <v>0</v>
       </c>
-      <c r="I11" t="n">
-        <v>7</v>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -6732,9 +6757,12 @@
           <t>msv6comjfd2xw</t>
         </is>
       </c>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -6747,17 +6775,17 @@
   <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51.83203125" customWidth="1" min="1" max="1"/>
-    <col width="55.83203125" customWidth="1" min="2" max="2"/>
-    <col width="19.83203125" customWidth="1" min="3" max="3"/>
-    <col width="14.83203125" customWidth="1" min="4" max="4"/>
-    <col width="14.83203125" customWidth="1" min="5" max="5"/>
-    <col width="10.83203125" customWidth="1" min="6" max="6"/>
-    <col width="10.83203125" customWidth="1" min="7" max="7"/>
-    <col width="10.83203125" customWidth="1" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" min="9" max="9"/>
-    <col width="13.83203125" customWidth="1" min="10" max="10"/>
-    <col width="15.83203125" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8304,7 +8332,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8356,7 +8384,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8407,7 +8435,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8462,7 +8490,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8516,7 +8544,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8579,7 +8607,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8599,7 +8627,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8612,10 +8640,10 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.83203125" customWidth="1" min="1" max="1"/>
-    <col width="10.83203125" customWidth="1" min="2" max="2"/>
-    <col width="55.83203125" customWidth="1" min="3" max="3"/>
-    <col width="15.83203125" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8729,18 +8757,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8782,7 +8815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09:00 - 10:15</t>
+          <t>04:00 - 05:15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8792,17 +8825,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Scikit-Learn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Installation Guide</t>
+          <t>API &amp; Core Architecture</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8810,12 +8843,16 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Must Know First, Learn Next, Explore Last</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10:15 - 10:30</t>
+          <t>05:15 - 05:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8830,7 +8867,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>☕ Rest &amp; Refresh Break</t>
+          <t>☕ Morning Refresh Break</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8843,12 +8880,11 @@
           <t>Break</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10:30 - 11:45</t>
+          <t>05:30 - 06:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8858,17 +8894,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Scikit-Learn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Building From Source</t>
+          <t>User Guide: Supervised Learning</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -8876,45 +8912,48 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1. Supervised learning, 2. Unsupervised learning</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11:45 - 12:00</t>
+          <t>06:45 - 07:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Break</t>
+          <t>Review &amp; Practice</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wellness</t>
+          <t>Scikit-Learn</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>☕ Rest &amp; Refresh Break</t>
+          <t>Morning Code Practice &amp; Notes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:00 - 13:15</t>
+          <t>11:30 - 12:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8929,7 +8968,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Get Started with XGBoost</t>
+          <t>Installation &amp; Quick Start</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8942,12 +8981,16 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Building From Source, Get Started with XGBoost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13:15 - 13:30</t>
+          <t>12:45 - 13:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8962,7 +9005,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>☕ Rest &amp; Refresh Break</t>
+          <t>☕ Mid-Day Stretch &amp; Rest</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8975,46 +9018,252 @@
           <t>Break</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13:30 - 14:00</t>
+          <t>13:00 - 14:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Deep Work</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>XGBoost Tutorials &amp; Boosted Trees</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Introduction to Boosted Trees, Introduction to Model IO, Slicing Models</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14:15 - 14:30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Review &amp; Practice</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>XGBoost Tutorials</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Model Serialization &amp; Parameters</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Introduction to Boosted Trees, Introduction to Model IO, Slicing Models</t>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16:00 - 17:10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deep Work</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Installation, Quickstart &amp; Local Server</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Install, Quickstart, Local server</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17:10 - 17:25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>☕ Evening Walk &amp; Refresh</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>17:25 - 18:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deep Work</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Thinking in LangGraph &amp; Workflows</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thinking in LangGraph, Workflows + agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>19:30 - 20:30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deep Work</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MCP Python SDK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MCP Servers &amp; Handler Architecture</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Get started, Servers, Inside your handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20:30 - 21:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wrap-Up &amp; Wind Down</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MCP Python SDK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Night Review &amp; Tomorrow Prep (Done by 9 PM)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>